--- a/StudentGuideModule2/what_labs_to_include/132 lab list for 2022spring.xlsx
+++ b/StudentGuideModule2/what_labs_to_include/132 lab list for 2022spring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtrawick\Desktop\github\132\StudentGuideModule2\what_labs_to_include\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8098BE-8D17-4738-BA37-2A660FA9B543}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007ABD95-A371-4920-A1C3-626C4868C1F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18780" yWindow="5136" windowWidth="26616" windowHeight="15936" tabRatio="541" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2344,9 +2344,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="16" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2548,6 +2545,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2976,1844 +2976,1844 @@
   <dimension ref="A1:AD122"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.77734375" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" style="22" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" style="13" customWidth="1"/>
-    <col min="5" max="6" width="5.77734375" style="13" customWidth="1"/>
-    <col min="7" max="7" width="30.109375" style="19" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" style="12" customWidth="1"/>
+    <col min="5" max="6" width="5.77734375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" style="18" customWidth="1"/>
     <col min="8" max="8" width="8.77734375" style="2" customWidth="1"/>
-    <col min="9" max="12" width="8.77734375" style="74" customWidth="1"/>
+    <col min="9" max="12" width="8.77734375" style="73" customWidth="1"/>
     <col min="13" max="13" width="8.77734375" style="2" customWidth="1"/>
-    <col min="14" max="15" width="8.77734375" style="74" customWidth="1"/>
-    <col min="16" max="19" width="8.77734375" style="83" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="74" customWidth="1"/>
+    <col min="14" max="15" width="8.77734375" style="73" customWidth="1"/>
+    <col min="16" max="19" width="8.77734375" style="82" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="73" customWidth="1"/>
     <col min="21" max="21" width="11" style="3" customWidth="1"/>
-    <col min="22" max="22" width="6.6640625" style="3" customWidth="1"/>
+    <col min="22" max="22" width="9.88671875" style="3" customWidth="1"/>
     <col min="23" max="23" width="10.33203125" style="3" customWidth="1"/>
     <col min="25" max="25" width="9.44140625" customWidth="1"/>
     <col min="26" max="26" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="H1" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="L1" s="46" t="s">
+      <c r="L1" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="N1" s="46" t="s">
+      <c r="N1" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="O1" s="46" t="s">
+      <c r="O1" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="P1" s="46" t="s">
+      <c r="P1" s="45" t="s">
         <v>235</v>
       </c>
-      <c r="Q1" s="46" t="s">
+      <c r="Q1" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="R1" s="49" t="s">
+      <c r="R1" s="48" t="s">
         <v>224</v>
       </c>
-      <c r="S1" s="30"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
     </row>
     <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="53">
+      <c r="C2" s="49"/>
+      <c r="D2" s="52">
         <v>4</v>
       </c>
-      <c r="E2" s="53">
-        <v>1</v>
-      </c>
-      <c r="F2" s="53">
-        <f>CEILING(D2,T$22+1)</f>
+      <c r="E2" s="52">
+        <v>1</v>
+      </c>
+      <c r="F2" s="52">
+        <f t="shared" ref="F2:F33" si="0">CEILING(D2,T$22+1)</f>
         <v>4</v>
       </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="55">
-        <v>1</v>
-      </c>
-      <c r="K2" s="52"/>
-      <c r="L2" s="87">
-        <v>1</v>
-      </c>
-      <c r="M2" s="87"/>
-      <c r="N2" s="55">
-        <v>1</v>
-      </c>
-      <c r="O2" s="52"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="78">
+      <c r="G2" s="53"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="54">
+        <v>1</v>
+      </c>
+      <c r="K2" s="51"/>
+      <c r="L2" s="86">
+        <v>1</v>
+      </c>
+      <c r="M2" s="86"/>
+      <c r="N2" s="54">
+        <v>1</v>
+      </c>
+      <c r="O2" s="51"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="77">
         <v>2</v>
       </c>
-      <c r="R2" s="66">
+      <c r="R2" s="65">
         <f>SUM(N2:Q2)</f>
         <v>3</v>
       </c>
-      <c r="S2" s="31"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="45"/>
-      <c r="B3" s="51" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="57">
+      <c r="C3" s="50"/>
+      <c r="D3" s="56">
         <v>2</v>
       </c>
-      <c r="E3" s="57">
-        <v>0</v>
-      </c>
-      <c r="F3" s="57">
-        <f>CEILING(D3,T$22+1)</f>
-        <v>2</v>
-      </c>
-      <c r="G3" s="58"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="56">
-        <v>1</v>
-      </c>
-      <c r="K3" s="56"/>
-      <c r="L3" s="88">
-        <v>1</v>
-      </c>
-      <c r="M3" s="88"/>
-      <c r="N3" s="56">
-        <v>1</v>
-      </c>
-      <c r="O3" s="56"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="79">
-        <v>2</v>
-      </c>
-      <c r="R3" s="80">
-        <f t="shared" ref="R3:R66" si="0">SUM(N3:Q3)</f>
-        <v>3</v>
-      </c>
-      <c r="S3" s="31"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="31"/>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="31"/>
-    </row>
-    <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="D4" s="13">
-        <v>5</v>
-      </c>
-      <c r="E4" s="13">
-        <v>0</v>
-      </c>
-      <c r="F4" s="13">
-        <f>CEILING(D4,T$22+1)</f>
-        <v>6</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="76">
-        <v>1</v>
-      </c>
-      <c r="I4" s="76">
-        <v>1</v>
-      </c>
-      <c r="J4" s="76">
-        <v>1</v>
-      </c>
-      <c r="K4" s="34">
-        <v>1</v>
-      </c>
-      <c r="L4" s="84">
-        <v>1</v>
-      </c>
-      <c r="M4" s="84">
-        <v>1</v>
-      </c>
-      <c r="N4" s="84"/>
-      <c r="O4" s="84">
-        <v>1</v>
-      </c>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S4" s="31"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B5" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="13">
-        <v>2</v>
-      </c>
-      <c r="E5" s="13">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13">
-        <f>CEILING(D5,T$22+1)</f>
-        <v>2</v>
-      </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="74">
-        <v>1</v>
-      </c>
-      <c r="I5" s="74">
-        <v>1</v>
-      </c>
-      <c r="J5" s="76">
-        <v>1</v>
-      </c>
-      <c r="K5" s="72">
-        <v>1</v>
-      </c>
-      <c r="L5" s="83">
-        <v>1</v>
-      </c>
-      <c r="M5" s="83">
-        <v>1</v>
-      </c>
-      <c r="N5" s="84"/>
-      <c r="O5" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S5" s="31"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="31"/>
-      <c r="Z5" s="31"/>
-      <c r="AA5" s="31"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D6" s="13">
-        <v>2</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13">
-        <f>CEILING(D6,T$22+1)</f>
-        <v>2</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="H6" s="76">
-        <v>1</v>
-      </c>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76">
-        <v>1</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="84">
-        <v>1</v>
-      </c>
-      <c r="P6" s="84"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S6" s="31"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
-      <c r="AA6" s="31"/>
-    </row>
-    <row r="7" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="45"/>
-      <c r="B7" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="26">
-        <v>1</v>
-      </c>
-      <c r="E7" s="26">
-        <v>0</v>
-      </c>
-      <c r="F7" s="26">
-        <f>CEILING(D7,T$22+1)</f>
-        <v>2</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77">
-        <v>1</v>
-      </c>
-      <c r="K7" s="73"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="86"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="80">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="14"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D8" s="13">
-        <v>4</v>
-      </c>
-      <c r="E8" s="13">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13">
-        <f>CEILING(D8,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="H8" s="74">
-        <v>1</v>
-      </c>
-      <c r="I8" s="74">
-        <v>1</v>
-      </c>
-      <c r="J8" s="76">
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="32">
-        <v>1</v>
-      </c>
-      <c r="L8" s="82"/>
-      <c r="M8" s="83">
-        <v>1</v>
-      </c>
-      <c r="N8" s="84">
-        <v>1</v>
-      </c>
-      <c r="O8" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="66">
+      <c r="E3" s="56">
+        <v>0</v>
+      </c>
+      <c r="F3" s="56">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="S8" s="31"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="31"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="55">
+        <v>1</v>
+      </c>
+      <c r="K3" s="55"/>
+      <c r="L3" s="87">
+        <v>1</v>
+      </c>
+      <c r="M3" s="87"/>
+      <c r="N3" s="55">
+        <v>1</v>
+      </c>
+      <c r="O3" s="55"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="78">
+        <v>2</v>
+      </c>
+      <c r="R3" s="79">
+        <f t="shared" ref="R3:R66" si="1">SUM(N3:Q3)</f>
+        <v>3</v>
+      </c>
+      <c r="S3" s="30"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+    </row>
+    <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="12">
+        <v>5</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4" s="75">
+        <v>1</v>
+      </c>
+      <c r="I4" s="75">
+        <v>1</v>
+      </c>
+      <c r="J4" s="75">
+        <v>1</v>
+      </c>
+      <c r="K4" s="33">
+        <v>1</v>
+      </c>
+      <c r="L4" s="83">
+        <v>1</v>
+      </c>
+      <c r="M4" s="83">
+        <v>1</v>
+      </c>
+      <c r="N4" s="83"/>
+      <c r="O4" s="83">
+        <v>1</v>
+      </c>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S4" s="30"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B5" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="12">
+        <v>2</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="73">
+        <v>1</v>
+      </c>
+      <c r="I5" s="73">
+        <v>1</v>
+      </c>
+      <c r="J5" s="75">
+        <v>1</v>
+      </c>
+      <c r="K5" s="71">
+        <v>1</v>
+      </c>
+      <c r="L5" s="82">
+        <v>1</v>
+      </c>
+      <c r="M5" s="82">
+        <v>1</v>
+      </c>
+      <c r="N5" s="83"/>
+      <c r="O5" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S5" s="30"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A6" s="27"/>
+      <c r="B6" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="12">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="75">
+        <v>1</v>
+      </c>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83">
+        <v>1</v>
+      </c>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="75"/>
+      <c r="R6" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S6" s="30"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+    </row>
+    <row r="7" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="44"/>
+      <c r="B7" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="25">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25">
+        <v>0</v>
+      </c>
+      <c r="F7" s="25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="76">
+        <v>1</v>
+      </c>
+      <c r="K7" s="72"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="76"/>
+      <c r="R7" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="13"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A8" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="12">
+        <v>4</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="H8" s="73">
+        <v>1</v>
+      </c>
+      <c r="I8" s="73">
+        <v>1</v>
+      </c>
+      <c r="J8" s="75">
+        <v>0.1</v>
+      </c>
+      <c r="K8" s="31">
+        <v>1</v>
+      </c>
+      <c r="L8" s="81"/>
+      <c r="M8" s="82">
+        <v>1</v>
+      </c>
+      <c r="N8" s="83">
+        <v>1</v>
+      </c>
+      <c r="O8" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="65">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S8" s="30"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>2</v>
       </c>
-      <c r="E9" s="13">
-        <v>0</v>
-      </c>
-      <c r="F9" s="13">
-        <f>CEILING(D9,T$22+1)</f>
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="74">
-        <v>1</v>
-      </c>
-      <c r="I9" s="74">
-        <v>1</v>
-      </c>
-      <c r="J9" s="76">
-        <v>1</v>
-      </c>
-      <c r="K9" s="32">
-        <v>1</v>
-      </c>
-      <c r="L9" s="83">
-        <v>1</v>
-      </c>
-      <c r="M9" s="83"/>
-      <c r="N9" s="84"/>
-      <c r="O9" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="66">
+      <c r="H9" s="73">
+        <v>1</v>
+      </c>
+      <c r="I9" s="73">
+        <v>1</v>
+      </c>
+      <c r="J9" s="75">
+        <v>1</v>
+      </c>
+      <c r="K9" s="31">
+        <v>1</v>
+      </c>
+      <c r="L9" s="82">
+        <v>1</v>
+      </c>
+      <c r="M9" s="82"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S9" s="30"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+    </row>
+    <row r="10" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D10" s="12">
+        <v>5</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S9" s="31"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="31"/>
-      <c r="AA9" s="31"/>
-    </row>
-    <row r="10" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="73"/>
+      <c r="J10" s="75">
+        <v>0</v>
+      </c>
+      <c r="K10" s="30"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="82">
+        <v>1</v>
+      </c>
+      <c r="N10" s="83">
+        <v>0.5</v>
+      </c>
+      <c r="O10" s="82"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="65">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="S10" s="30"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B11" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D10" s="13">
-        <v>5</v>
-      </c>
-      <c r="E10" s="13">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
-        <f>CEILING(D10,T$22+1)</f>
-        <v>6</v>
-      </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="74"/>
-      <c r="J10" s="76">
-        <v>0</v>
-      </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="83">
-        <v>1</v>
-      </c>
-      <c r="N10" s="84">
-        <v>0.5</v>
-      </c>
-      <c r="O10" s="83"/>
-      <c r="Q10" s="74"/>
-      <c r="R10" s="66">
+      <c r="D11" s="12">
+        <v>2</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="S10" s="31"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="31"/>
-      <c r="AA10" s="31"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D11" s="13">
         <v>2</v>
       </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
-        <f>CEILING(D11,T$22+1)</f>
-        <v>2</v>
-      </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H11" s="74">
-        <v>1</v>
-      </c>
-      <c r="I11" s="74">
-        <v>1</v>
-      </c>
-      <c r="J11" s="76">
-        <v>1</v>
-      </c>
-      <c r="K11" s="32">
-        <v>1</v>
-      </c>
-      <c r="L11" s="82"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="84"/>
-      <c r="O11" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="66">
+      <c r="H11" s="73">
+        <v>1</v>
+      </c>
+      <c r="I11" s="73">
+        <v>1</v>
+      </c>
+      <c r="J11" s="75">
+        <v>1</v>
+      </c>
+      <c r="K11" s="31">
+        <v>1</v>
+      </c>
+      <c r="L11" s="81"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="73"/>
+      <c r="R11" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S11" s="30"/>
+      <c r="T11" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="U11" s="40"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+    </row>
+    <row r="12" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="12">
+        <v>4</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S11" s="31"/>
-      <c r="T11" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="U11" s="41"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="31"/>
-      <c r="Z11" s="31"/>
-      <c r="AA11" s="31"/>
-    </row>
-    <row r="12" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="H12" s="73"/>
+      <c r="J12" s="75">
+        <v>0</v>
+      </c>
+      <c r="L12" s="82">
+        <v>1</v>
+      </c>
+      <c r="M12" s="82">
+        <v>1</v>
+      </c>
+      <c r="N12" s="83">
+        <v>1</v>
+      </c>
+      <c r="O12" s="82"/>
+      <c r="Q12" s="73"/>
+      <c r="R12" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S12" s="30"/>
+      <c r="T12" s="41">
+        <v>1.5</v>
+      </c>
+      <c r="U12" s="42"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B13" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D13" s="12">
+        <v>3</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E12" s="13">
-        <v>1</v>
-      </c>
-      <c r="F12" s="13">
-        <f>CEILING(D12,T$22+1)</f>
+      <c r="G13" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="H13" s="73"/>
+      <c r="J13" s="75">
+        <v>0</v>
+      </c>
+      <c r="L13" s="82">
+        <v>1</v>
+      </c>
+      <c r="M13" s="82">
+        <v>1</v>
+      </c>
+      <c r="N13" s="83">
+        <v>1</v>
+      </c>
+      <c r="O13" s="82"/>
+      <c r="Q13" s="73"/>
+      <c r="R13" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
+    </row>
+    <row r="14" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="12">
+        <v>3</v>
+      </c>
+      <c r="E14" s="12">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G12" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="H12" s="74"/>
-      <c r="J12" s="76">
-        <v>0</v>
-      </c>
-      <c r="L12" s="83">
-        <v>1</v>
-      </c>
-      <c r="M12" s="83">
-        <v>1</v>
-      </c>
-      <c r="N12" s="84">
-        <v>1</v>
-      </c>
-      <c r="O12" s="83"/>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S12" s="31"/>
-      <c r="T12" s="42">
-        <v>1.5</v>
-      </c>
-      <c r="U12" s="43"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="31"/>
-      <c r="AA12" s="31"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="D13" s="13">
-        <v>3</v>
-      </c>
-      <c r="E13" s="13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13">
-        <f>CEILING(D13,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="H13" s="74"/>
-      <c r="J13" s="76">
-        <v>0</v>
-      </c>
-      <c r="L13" s="83">
-        <v>1</v>
-      </c>
-      <c r="M13" s="83">
-        <v>1</v>
-      </c>
-      <c r="N13" s="84">
-        <v>1</v>
-      </c>
-      <c r="O13" s="83"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="31"/>
-    </row>
-    <row r="14" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="D14" s="13">
-        <v>3</v>
-      </c>
-      <c r="E14" s="13">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13">
-        <f>CEILING(D14,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="H14" s="74"/>
-      <c r="J14" s="76"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="84"/>
-      <c r="O14" s="83"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="31"/>
+      <c r="H14" s="73"/>
+      <c r="J14" s="75"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="82"/>
+      <c r="N14" s="83"/>
+      <c r="O14" s="82"/>
+      <c r="Q14" s="73"/>
+      <c r="R14" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="30"/>
       <c r="T14" s="1" t="s">
         <v>89</v>
       </c>
       <c r="U14"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="31"/>
-      <c r="Z14" s="31"/>
-      <c r="AA14" s="31"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <v>3</v>
       </c>
-      <c r="E15" s="13">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
-        <f>CEILING(D15,T$22+1)</f>
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="H15" s="74"/>
-      <c r="J15" s="76"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="83"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="83"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="66">
+      <c r="H15" s="73"/>
+      <c r="J15" s="75"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="82"/>
+      <c r="N15" s="83"/>
+      <c r="O15" s="82"/>
+      <c r="Q15" s="73"/>
+      <c r="R15" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="30"/>
+      <c r="T15" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="U15" s="35"/>
+      <c r="V15" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="W15" s="30"/>
+      <c r="X15" s="30"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
+      <c r="AA15" s="30"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B16" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="12">
+        <v>9</v>
+      </c>
+      <c r="E16" s="12">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="31"/>
-      <c r="T15" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="U15" s="36"/>
-      <c r="V15" s="15">
+        <v>10</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" s="73">
+        <v>1</v>
+      </c>
+      <c r="I16" s="73">
+        <v>1</v>
+      </c>
+      <c r="J16" s="75">
+        <v>1</v>
+      </c>
+      <c r="K16" s="31">
+        <v>1</v>
+      </c>
+      <c r="L16" s="82">
+        <v>1</v>
+      </c>
+      <c r="M16" s="82">
+        <v>1</v>
+      </c>
+      <c r="N16" s="83">
+        <v>1</v>
+      </c>
+      <c r="O16" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="73"/>
+      <c r="R16" s="65">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S16" s="30"/>
+      <c r="T16" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="U16" s="4"/>
+      <c r="V16" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
+      <c r="AA16" s="30"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B17" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" s="12">
+        <v>3</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G17" s="20"/>
+      <c r="H17" s="73">
+        <v>1</v>
+      </c>
+      <c r="I17" s="73">
+        <v>1</v>
+      </c>
+      <c r="J17" s="75">
+        <v>1</v>
+      </c>
+      <c r="K17" s="31">
+        <v>1</v>
+      </c>
+      <c r="L17" s="82">
+        <v>1</v>
+      </c>
+      <c r="M17" s="82">
+        <v>1</v>
+      </c>
+      <c r="N17" s="83">
+        <v>1</v>
+      </c>
+      <c r="O17" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="73"/>
+      <c r="R17" s="65">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S17" s="30"/>
+      <c r="T17" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="U17" s="4"/>
+      <c r="V17" s="7">
+        <v>3</v>
+      </c>
+      <c r="W17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="30"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B18" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18" s="12">
+        <v>5</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="H18" s="73">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="75">
+        <v>1</v>
+      </c>
+      <c r="K18" s="31">
+        <v>0</v>
+      </c>
+      <c r="L18" s="82">
+        <v>1</v>
+      </c>
+      <c r="M18" s="82">
+        <v>0</v>
+      </c>
+      <c r="N18" s="83"/>
+      <c r="O18" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="73"/>
+      <c r="R18" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S18" s="30"/>
+      <c r="T18" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="U18" s="4"/>
+      <c r="V18" s="36">
+        <v>0.25</v>
+      </c>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+    </row>
+    <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D19" s="12">
+        <v>4</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="73">
+        <v>1</v>
+      </c>
+      <c r="I19" s="73">
+        <v>1</v>
+      </c>
+      <c r="J19" s="75">
+        <v>1</v>
+      </c>
+      <c r="K19" s="31">
+        <v>0</v>
+      </c>
+      <c r="L19" s="82">
+        <v>0.1</v>
+      </c>
+      <c r="M19" s="82">
+        <v>1</v>
+      </c>
+      <c r="N19" s="83">
+        <v>1</v>
+      </c>
+      <c r="O19" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="73"/>
+      <c r="R19" s="65">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S19" s="30"/>
+      <c r="T19" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="U19" s="37"/>
+      <c r="V19" s="38">
         <v>0.05</v>
       </c>
-      <c r="W15" s="31"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="31"/>
-      <c r="AA15" s="31"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="29" t="s">
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
+      <c r="AA19" s="30"/>
+    </row>
+    <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D16" s="13">
-        <v>9</v>
-      </c>
-      <c r="E16" s="13">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13">
-        <f>CEILING(D16,T$22+1)</f>
-        <v>10</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="H16" s="74">
-        <v>1</v>
-      </c>
-      <c r="I16" s="74">
-        <v>1</v>
-      </c>
-      <c r="J16" s="76">
-        <v>1</v>
-      </c>
-      <c r="K16" s="32">
-        <v>1</v>
-      </c>
-      <c r="L16" s="83">
-        <v>1</v>
-      </c>
-      <c r="M16" s="83">
-        <v>1</v>
-      </c>
-      <c r="N16" s="84">
-        <v>1</v>
-      </c>
-      <c r="O16" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="66">
+      <c r="D20" s="12">
+        <v>5</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12">
         <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="73">
+        <v>1</v>
+      </c>
+      <c r="I20" s="73">
+        <v>1</v>
+      </c>
+      <c r="J20" s="75">
+        <v>1</v>
+      </c>
+      <c r="K20" s="31">
+        <v>1</v>
+      </c>
+      <c r="L20" s="82">
+        <v>1</v>
+      </c>
+      <c r="M20" s="82">
+        <v>1</v>
+      </c>
+      <c r="N20" s="83">
+        <v>1</v>
+      </c>
+      <c r="O20" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="65">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S16" s="31"/>
-      <c r="T16" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="U16" s="5"/>
-      <c r="V16" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-      <c r="AA16" s="31"/>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B17" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D17" s="13">
-        <v>3</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13">
-        <f>CEILING(D17,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="74">
-        <v>1</v>
-      </c>
-      <c r="I17" s="74">
-        <v>1</v>
-      </c>
-      <c r="J17" s="76">
-        <v>1</v>
-      </c>
-      <c r="K17" s="32">
-        <v>1</v>
-      </c>
-      <c r="L17" s="83">
-        <v>1</v>
-      </c>
-      <c r="M17" s="83">
-        <v>1</v>
-      </c>
-      <c r="N17" s="84">
-        <v>1</v>
-      </c>
-      <c r="O17" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="66">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="S17" s="31"/>
-      <c r="T17" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="U17" s="5"/>
-      <c r="V17" s="8">
-        <v>3</v>
-      </c>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B18" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="D18" s="13">
-        <v>5</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13">
-        <f>CEILING(D18,T$22+1)</f>
-        <v>6</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="H18" s="74">
-        <v>0.5</v>
-      </c>
-      <c r="J18" s="76">
-        <v>1</v>
-      </c>
-      <c r="K18" s="32">
-        <v>0</v>
-      </c>
-      <c r="L18" s="83">
-        <v>1</v>
-      </c>
-      <c r="M18" s="83">
-        <v>0</v>
-      </c>
-      <c r="N18" s="84"/>
-      <c r="O18" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S18" s="31"/>
-      <c r="T18" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="U18" s="5"/>
-      <c r="V18" s="37">
-        <v>0.25</v>
-      </c>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="31"/>
-      <c r="AA18" s="31"/>
-    </row>
-    <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D19" s="13">
-        <v>4</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13">
-        <f>CEILING(D19,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="H19" s="74">
-        <v>1</v>
-      </c>
-      <c r="I19" s="74">
-        <v>1</v>
-      </c>
-      <c r="J19" s="76">
-        <v>1</v>
-      </c>
-      <c r="K19" s="32">
-        <v>0</v>
-      </c>
-      <c r="L19" s="83">
-        <v>0.1</v>
-      </c>
-      <c r="M19" s="83">
-        <v>1</v>
-      </c>
-      <c r="N19" s="84">
-        <v>1</v>
-      </c>
-      <c r="O19" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="66">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="S19" s="31"/>
-      <c r="T19" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="U19" s="38"/>
-      <c r="V19" s="39">
-        <v>0.05</v>
-      </c>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="31"/>
-      <c r="AA19" s="31"/>
-    </row>
-    <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D20" s="13">
-        <v>5</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
-        <f>CEILING(D20,T$22+1)</f>
-        <v>6</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="74">
-        <v>1</v>
-      </c>
-      <c r="I20" s="74">
-        <v>1</v>
-      </c>
-      <c r="J20" s="76">
-        <v>1</v>
-      </c>
-      <c r="K20" s="32">
-        <v>1</v>
-      </c>
-      <c r="L20" s="83">
-        <v>1</v>
-      </c>
-      <c r="M20" s="83">
-        <v>1</v>
-      </c>
-      <c r="N20" s="84">
-        <v>1</v>
-      </c>
-      <c r="O20" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="66">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="S20" s="31"/>
+      <c r="S20" s="30"/>
       <c r="T20" s="3"/>
       <c r="U20"/>
       <c r="V20"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="31"/>
-      <c r="AA20" s="31"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <v>3</v>
       </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
-        <f>CEILING(D21,T$22+1)</f>
+      <c r="E21" s="12">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="74"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="84"/>
-      <c r="O21" s="83"/>
-      <c r="Q21" s="74"/>
-      <c r="R21" s="66">
+      <c r="G21" s="20"/>
+      <c r="H21" s="73"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="82"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="82"/>
+      <c r="Q21" s="73"/>
+      <c r="R21" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="30"/>
+      <c r="T21" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="U21" s="40"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+      <c r="AA21" s="30"/>
+    </row>
+    <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="12">
+        <v>4</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0</v>
+      </c>
+      <c r="F22" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="31"/>
-      <c r="T21" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="U21" s="41"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="31"/>
-      <c r="Z21" s="31"/>
-      <c r="AA21" s="31"/>
-    </row>
-    <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="13">
         <v>4</v>
       </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13">
-        <f>CEILING(D22,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G22" s="21"/>
-      <c r="H22" s="74"/>
-      <c r="J22" s="76">
+      <c r="G22" s="20"/>
+      <c r="H22" s="73"/>
+      <c r="J22" s="75">
         <v>0.1</v>
       </c>
-      <c r="K22" s="32">
-        <v>0</v>
-      </c>
-      <c r="L22" s="82"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="83"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="31"/>
-      <c r="T22" s="42">
-        <v>1</v>
-      </c>
-      <c r="U22" s="43"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
-      <c r="AA22" s="31"/>
+      <c r="K22" s="31">
+        <v>0</v>
+      </c>
+      <c r="L22" s="81"/>
+      <c r="M22" s="82"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="82"/>
+      <c r="Q22" s="73"/>
+      <c r="R22" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="30"/>
+      <c r="T22" s="41">
+        <v>1</v>
+      </c>
+      <c r="U22" s="42"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="30"/>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <v>2</v>
       </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
-        <f>CEILING(D23,T$22+1)</f>
-        <v>2</v>
-      </c>
-      <c r="G23" s="21"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74">
-        <v>1</v>
-      </c>
-      <c r="J23" s="76">
-        <v>0</v>
-      </c>
-      <c r="K23" s="32">
-        <v>1</v>
-      </c>
-      <c r="L23" s="83">
-        <v>1</v>
-      </c>
-      <c r="M23" s="83">
-        <v>0.5</v>
-      </c>
-      <c r="N23" s="84"/>
-      <c r="O23" s="83"/>
-      <c r="Q23" s="77"/>
-      <c r="R23" s="80">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="31"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-    </row>
-    <row r="24" spans="1:27" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="D24" s="12">
-        <v>10</v>
-      </c>
-      <c r="E24" s="12">
-        <v>0</v>
-      </c>
-      <c r="F24" s="12">
-        <f>CEILING(D24,T$22+1)</f>
-        <v>10</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="I24" s="75">
-        <v>1</v>
-      </c>
-      <c r="J24" s="75">
-        <v>1</v>
-      </c>
-      <c r="K24" s="33">
-        <v>1</v>
-      </c>
-      <c r="L24" s="85">
-        <v>1</v>
-      </c>
-      <c r="M24" s="85">
-        <v>1</v>
-      </c>
-      <c r="N24" s="85">
-        <v>1</v>
-      </c>
-      <c r="O24" s="85">
-        <v>1</v>
-      </c>
-      <c r="P24" s="85"/>
-      <c r="Q24" s="76"/>
-      <c r="R24" s="66">
+      <c r="E23" s="12">
+        <v>0</v>
+      </c>
+      <c r="F23" s="12">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="S24" s="31"/>
-      <c r="T24" s="14"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
-      <c r="AA24" s="31"/>
-    </row>
-    <row r="25" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="22" t="s">
+      <c r="G23" s="20"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <v>1</v>
+      </c>
+      <c r="J23" s="75">
+        <v>0</v>
+      </c>
+      <c r="K23" s="31">
+        <v>1</v>
+      </c>
+      <c r="L23" s="82">
+        <v>1</v>
+      </c>
+      <c r="M23" s="82">
+        <v>0.5</v>
+      </c>
+      <c r="N23" s="83"/>
+      <c r="O23" s="82"/>
+      <c r="Q23" s="76"/>
+      <c r="R23" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="30"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+    </row>
+    <row r="24" spans="1:27" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="11">
+        <v>10</v>
+      </c>
+      <c r="E24" s="11">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="74">
+        <v>0.5</v>
+      </c>
+      <c r="I24" s="74">
+        <v>1</v>
+      </c>
+      <c r="J24" s="74">
+        <v>1</v>
+      </c>
+      <c r="K24" s="32">
+        <v>1</v>
+      </c>
+      <c r="L24" s="84">
+        <v>1</v>
+      </c>
+      <c r="M24" s="84">
+        <v>1</v>
+      </c>
+      <c r="N24" s="84">
+        <v>1</v>
+      </c>
+      <c r="O24" s="84">
+        <v>1</v>
+      </c>
+      <c r="P24" s="84"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="65">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S24" s="30"/>
+      <c r="T24" s="13"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B25" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <v>8</v>
       </c>
-      <c r="E25" s="13">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13">
-        <f>CEILING(D25,T$22+1)</f>
+      <c r="E25" s="12">
+        <v>0</v>
+      </c>
+      <c r="F25" s="12">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="G25" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H25" s="74">
-        <v>1</v>
-      </c>
-      <c r="I25" s="74">
-        <v>1</v>
-      </c>
-      <c r="J25" s="76">
-        <v>1</v>
-      </c>
-      <c r="K25" s="32">
-        <v>1</v>
-      </c>
-      <c r="L25" s="83">
-        <v>1</v>
-      </c>
-      <c r="M25" s="83">
-        <v>1</v>
-      </c>
-      <c r="N25" s="84">
-        <v>1</v>
-      </c>
-      <c r="O25" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="74"/>
-      <c r="R25" s="66">
-        <f t="shared" si="0"/>
+      <c r="H25" s="73">
+        <v>1</v>
+      </c>
+      <c r="I25" s="73">
+        <v>1</v>
+      </c>
+      <c r="J25" s="75">
+        <v>1</v>
+      </c>
+      <c r="K25" s="31">
+        <v>1</v>
+      </c>
+      <c r="L25" s="82">
+        <v>1</v>
+      </c>
+      <c r="M25" s="82">
+        <v>1</v>
+      </c>
+      <c r="N25" s="83">
+        <v>1</v>
+      </c>
+      <c r="O25" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="73"/>
+      <c r="R25" s="65">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S25" s="31"/>
-      <c r="T25" s="89" t="s">
+      <c r="S25" s="30"/>
+      <c r="T25" s="88" t="s">
         <v>165</v>
       </c>
-      <c r="U25" s="4" t="s">
+      <c r="U25" s="89" t="s">
         <v>166</v>
       </c>
-      <c r="V25" s="4" t="s">
+      <c r="V25" s="89" t="s">
         <v>167</v>
       </c>
-      <c r="W25" s="7" t="s">
+      <c r="W25" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-      <c r="AA25" s="31"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
+      <c r="AA25" s="30"/>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>223</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="12">
         <v>3</v>
       </c>
-      <c r="E26" s="13">
-        <v>0</v>
-      </c>
-      <c r="F26" s="13">
-        <f>CEILING(D26,T$22+1)</f>
+      <c r="E26" s="12">
+        <v>0</v>
+      </c>
+      <c r="F26" s="12">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="G26" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="H26" s="74"/>
-      <c r="J26" s="76">
-        <v>1</v>
-      </c>
-      <c r="K26" s="74">
-        <v>1</v>
-      </c>
-      <c r="L26" s="82"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="83"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="31"/>
-      <c r="T26" s="68">
-        <v>0</v>
-      </c>
-      <c r="U26" s="6">
+      <c r="H26" s="73"/>
+      <c r="J26" s="75">
+        <v>1</v>
+      </c>
+      <c r="K26" s="73">
+        <v>1</v>
+      </c>
+      <c r="L26" s="81"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="83"/>
+      <c r="O26" s="82"/>
+      <c r="Q26" s="73"/>
+      <c r="R26" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="30"/>
+      <c r="T26" s="67">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5">
         <f>SUMIF(R$2:R$85,"&gt;=" &amp; T26,F$2:F$85)</f>
         <v>370</v>
       </c>
-      <c r="V26" s="6">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T26,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W26" s="8">
-        <f>($V$17 + $V$15*U26+$V$16*V26)*(1+V$18+V$19)</f>
+      <c r="V26" s="5">
+        <f t="shared" ref="V26:V34" si="2">SUMIF(U$2:U$86,"&gt;=" &amp; T26,E$2:E$86)</f>
+        <v>0</v>
+      </c>
+      <c r="W26" s="7">
+        <f t="shared" ref="W26:W34" si="3">($V$17 + $V$15*U26+$V$16*V26)*(1+V$18+V$19)</f>
         <v>27.95</v>
       </c>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="12">
         <v>3</v>
       </c>
-      <c r="E27" s="13">
-        <v>0</v>
-      </c>
-      <c r="F27" s="13">
-        <f>CEILING(D27,T$22+1)</f>
+      <c r="E27" s="12">
+        <v>0</v>
+      </c>
+      <c r="F27" s="12">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G27" s="21"/>
-      <c r="H27" s="74">
-        <v>1</v>
-      </c>
-      <c r="J27" s="76">
-        <v>0</v>
-      </c>
-      <c r="K27" s="74">
-        <v>1</v>
-      </c>
-      <c r="L27" s="82"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="83"/>
-      <c r="Q27" s="74"/>
-      <c r="R27" s="66">
+      <c r="G27" s="20"/>
+      <c r="H27" s="73">
+        <v>1</v>
+      </c>
+      <c r="J27" s="75">
+        <v>0</v>
+      </c>
+      <c r="K27" s="73">
+        <v>1</v>
+      </c>
+      <c r="L27" s="81"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="83"/>
+      <c r="O27" s="82"/>
+      <c r="Q27" s="73"/>
+      <c r="R27" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="30"/>
+      <c r="T27" s="67">
+        <v>0.5</v>
+      </c>
+      <c r="U27" s="5">
+        <f t="shared" ref="U27:U34" si="4">SUMIF(R$2:R$85,"&gt;=" &amp; T27,F$2:F$85)</f>
+        <v>254</v>
+      </c>
+      <c r="V27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="7">
+        <f t="shared" si="3"/>
+        <v>20.410000000000004</v>
+      </c>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+    </row>
+    <row r="28" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="12">
+        <v>3</v>
+      </c>
+      <c r="E28" s="12">
+        <v>0</v>
+      </c>
+      <c r="F28" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="31"/>
-      <c r="T27" s="68">
+        <v>4</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="73">
         <v>0.5</v>
       </c>
-      <c r="U27" s="6">
-        <f t="shared" ref="U27:U34" si="1">SUMIF(R$2:R$85,"&gt;=" &amp; T27,F$2:F$85)</f>
-        <v>254</v>
-      </c>
-      <c r="V27" s="6">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T27,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W27" s="8">
-        <f>($V$17 + $V$15*U27+$V$16*V27)*(1+V$18+V$19)</f>
-        <v>20.410000000000004</v>
-      </c>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31"/>
-    </row>
-    <row r="28" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
-      <c r="B28" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="29" t="s">
+      <c r="I28" s="73">
+        <v>1</v>
+      </c>
+      <c r="J28" s="75">
+        <v>1</v>
+      </c>
+      <c r="K28" s="31">
+        <v>1</v>
+      </c>
+      <c r="L28" s="82"/>
+      <c r="M28" s="82">
+        <v>1</v>
+      </c>
+      <c r="N28" s="83">
+        <v>1</v>
+      </c>
+      <c r="O28" s="82">
+        <v>1</v>
+      </c>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="73"/>
+      <c r="R28" s="65">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T28" s="67">
+        <v>1</v>
+      </c>
+      <c r="U28" s="5">
+        <f t="shared" si="4"/>
+        <v>244</v>
+      </c>
+      <c r="V28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="7">
+        <f t="shared" si="3"/>
+        <v>19.760000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B29" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D29" s="12">
         <v>3</v>
       </c>
-      <c r="E28" s="13">
-        <v>0</v>
-      </c>
-      <c r="F28" s="13">
-        <f>CEILING(D28,T$22+1)</f>
+      <c r="E29" s="12">
+        <v>0</v>
+      </c>
+      <c r="F29" s="12">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="G29" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H28" s="74">
-        <v>0.5</v>
-      </c>
-      <c r="I28" s="74">
-        <v>1</v>
-      </c>
-      <c r="J28" s="76">
-        <v>1</v>
-      </c>
-      <c r="K28" s="32">
-        <v>1</v>
-      </c>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83">
-        <v>1</v>
-      </c>
-      <c r="N28" s="84">
-        <v>1</v>
-      </c>
-      <c r="O28" s="83">
-        <v>1</v>
-      </c>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="66">
+      <c r="H29" s="73">
+        <v>1</v>
+      </c>
+      <c r="I29" s="73">
+        <v>1</v>
+      </c>
+      <c r="J29" s="75">
+        <v>1</v>
+      </c>
+      <c r="K29" s="31">
+        <v>1</v>
+      </c>
+      <c r="L29" s="82">
+        <v>1</v>
+      </c>
+      <c r="M29" s="82"/>
+      <c r="N29" s="83"/>
+      <c r="O29" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="73"/>
+      <c r="R29" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S29" s="30"/>
+      <c r="T29" s="68">
+        <v>1.5</v>
+      </c>
+      <c r="U29" s="28">
+        <f t="shared" si="4"/>
+        <v>106</v>
+      </c>
+      <c r="V29" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="7">
+        <f t="shared" si="3"/>
+        <v>10.790000000000001</v>
+      </c>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B30" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="12">
+        <v>5</v>
+      </c>
+      <c r="E30" s="12">
+        <v>0</v>
+      </c>
+      <c r="F30" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="31">
+        <v>0</v>
+      </c>
+      <c r="L30" s="81"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="83"/>
+      <c r="O30" s="82"/>
+      <c r="Q30" s="73"/>
+      <c r="R30" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="30"/>
+      <c r="T30" s="67">
+        <v>2</v>
+      </c>
+      <c r="U30" s="5">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="V30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="7">
+        <f t="shared" si="3"/>
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="12">
+        <v>5</v>
+      </c>
+      <c r="E31" s="12">
+        <v>0</v>
+      </c>
+      <c r="F31" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G31" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H31" s="73"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="31">
+        <v>0</v>
+      </c>
+      <c r="L31" s="81"/>
+      <c r="M31" s="82"/>
+      <c r="N31" s="83"/>
+      <c r="O31" s="82"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="30"/>
+      <c r="T31" s="67">
+        <v>2.5</v>
+      </c>
+      <c r="U31" s="5">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="V31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="7">
+        <f t="shared" si="3"/>
+        <v>4.29</v>
+      </c>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="11">
+        <v>3</v>
+      </c>
+      <c r="E32" s="11">
+        <v>0</v>
+      </c>
+      <c r="F32" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="74"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="84"/>
+      <c r="O32" s="84"/>
+      <c r="P32" s="84"/>
+      <c r="Q32" s="75"/>
+      <c r="R32" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="30"/>
+      <c r="T32" s="67">
+        <v>3</v>
+      </c>
+      <c r="U32" s="5">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="V32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="7">
+        <f t="shared" si="3"/>
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D33" s="12">
+        <v>2</v>
+      </c>
+      <c r="E33" s="12">
+        <v>0</v>
+      </c>
+      <c r="F33" s="12">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="T28" s="68">
-        <v>1</v>
-      </c>
-      <c r="U28" s="6">
+      <c r="G33" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="73">
+        <v>1</v>
+      </c>
+      <c r="I33" s="73">
+        <v>1</v>
+      </c>
+      <c r="J33" s="75">
+        <v>1</v>
+      </c>
+      <c r="K33" s="71">
+        <v>1</v>
+      </c>
+      <c r="L33" s="82">
+        <v>1</v>
+      </c>
+      <c r="M33" s="82">
+        <v>1</v>
+      </c>
+      <c r="N33" s="83">
+        <v>1</v>
+      </c>
+      <c r="O33" s="82">
+        <v>1</v>
+      </c>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="73"/>
+      <c r="R33" s="65">
         <f t="shared" si="1"/>
-        <v>244</v>
-      </c>
-      <c r="V28" s="6">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T28,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W28" s="8">
-        <f>($V$17 + $V$15*U28+$V$16*V28)*(1+V$18+V$19)</f>
-        <v>19.760000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B29" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D29" s="13">
-        <v>3</v>
-      </c>
-      <c r="E29" s="13">
-        <v>0</v>
-      </c>
-      <c r="F29" s="13">
-        <f>CEILING(D29,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="74">
-        <v>1</v>
-      </c>
-      <c r="I29" s="74">
-        <v>1</v>
-      </c>
-      <c r="J29" s="76">
-        <v>1</v>
-      </c>
-      <c r="K29" s="32">
-        <v>1</v>
-      </c>
-      <c r="L29" s="83">
-        <v>1</v>
-      </c>
-      <c r="M29" s="83"/>
-      <c r="N29" s="84"/>
-      <c r="O29" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="74"/>
-      <c r="R29" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S29" s="31"/>
-      <c r="T29" s="69">
-        <v>1.5</v>
-      </c>
-      <c r="U29" s="29">
-        <f t="shared" si="1"/>
-        <v>106</v>
-      </c>
-      <c r="V29" s="29">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T29,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W29" s="8">
-        <f>($V$17 + $V$15*U29+$V$16*V29)*(1+V$18+V$19)</f>
-        <v>10.790000000000001</v>
-      </c>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B30" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D30" s="13">
-        <v>5</v>
-      </c>
-      <c r="E30" s="13">
-        <v>0</v>
-      </c>
-      <c r="F30" s="13">
-        <f>CEILING(D30,T$22+1)</f>
-        <v>6</v>
-      </c>
-      <c r="G30" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" s="74"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="32">
-        <v>0</v>
-      </c>
-      <c r="L30" s="82"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="84"/>
-      <c r="O30" s="83"/>
-      <c r="Q30" s="74"/>
-      <c r="R30" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="31"/>
-      <c r="T30" s="68">
         <v>2</v>
       </c>
-      <c r="U30" s="6">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="V30" s="6">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T30,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W30" s="8">
-        <f>($V$17 + $V$15*U30+$V$16*V30)*(1+V$18+V$19)</f>
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B31" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D31" s="13">
-        <v>5</v>
-      </c>
-      <c r="E31" s="13">
-        <v>0</v>
-      </c>
-      <c r="F31" s="13">
-        <f>CEILING(D31,T$22+1)</f>
-        <v>6</v>
-      </c>
-      <c r="G31" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="H31" s="74"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="32">
-        <v>0</v>
-      </c>
-      <c r="L31" s="82"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="84"/>
-      <c r="O31" s="83"/>
-      <c r="Q31" s="77"/>
-      <c r="R31" s="80">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="31"/>
-      <c r="T31" s="68">
-        <v>2.5</v>
-      </c>
-      <c r="U31" s="6">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="V31" s="6">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T31,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W31" s="8">
-        <f>($V$17 + $V$15*U31+$V$16*V31)*(1+V$18+V$19)</f>
-        <v>4.29</v>
-      </c>
-      <c r="X31" s="31"/>
-      <c r="Y31" s="31"/>
-      <c r="Z31" s="31"/>
-      <c r="AA31" s="31"/>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" s="12">
-        <v>3</v>
-      </c>
-      <c r="E32" s="12">
-        <v>0</v>
-      </c>
-      <c r="F32" s="12">
-        <f>CEILING(D32,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="85"/>
-      <c r="O32" s="85"/>
-      <c r="P32" s="85"/>
-      <c r="Q32" s="76"/>
-      <c r="R32" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="31"/>
-      <c r="T32" s="68">
-        <v>3</v>
-      </c>
-      <c r="U32" s="6">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="V32" s="6">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T32,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W32" s="8">
-        <f>($V$17 + $V$15*U32+$V$16*V32)*(1+V$18+V$19)</f>
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10"/>
-      <c r="B33" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D33" s="13">
-        <v>2</v>
-      </c>
-      <c r="E33" s="13">
-        <v>0</v>
-      </c>
-      <c r="F33" s="13">
-        <f>CEILING(D33,T$22+1)</f>
-        <v>2</v>
-      </c>
-      <c r="G33" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="H33" s="74">
-        <v>1</v>
-      </c>
-      <c r="I33" s="74">
-        <v>1</v>
-      </c>
-      <c r="J33" s="76">
-        <v>1</v>
-      </c>
-      <c r="K33" s="72">
-        <v>1</v>
-      </c>
-      <c r="L33" s="83">
-        <v>1</v>
-      </c>
-      <c r="M33" s="83">
-        <v>1</v>
-      </c>
-      <c r="N33" s="84">
-        <v>1</v>
-      </c>
-      <c r="O33" s="83">
-        <v>1</v>
-      </c>
-      <c r="P33" s="83"/>
-      <c r="Q33" s="74"/>
-      <c r="R33" s="66">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="S33" s="31"/>
-      <c r="T33" s="68">
+      <c r="S33" s="30"/>
+      <c r="T33" s="67">
         <v>3.5</v>
       </c>
-      <c r="U33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V33" s="6">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T33,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W33" s="8">
-        <f>($V$17 + $V$15*U33+$V$16*V33)*(1+V$18+V$19)</f>
+      <c r="U33" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="7">
+        <f t="shared" si="3"/>
         <v>3.9000000000000004</v>
       </c>
       <c r="X33"/>
@@ -4822,490 +4822,490 @@
       <c r="AA33"/>
     </row>
     <row r="34" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="13">
-        <v>1</v>
-      </c>
-      <c r="E34" s="13">
-        <v>0</v>
-      </c>
-      <c r="F34" s="13">
-        <f>CEILING(D34,T$22+1)</f>
+      <c r="D34" s="12">
+        <v>1</v>
+      </c>
+      <c r="E34" s="12">
+        <v>0</v>
+      </c>
+      <c r="F34" s="12">
+        <f t="shared" ref="F34:F65" si="5">CEILING(D34,T$22+1)</f>
         <v>2</v>
       </c>
-      <c r="G34" s="21" t="s">
+      <c r="G34" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="H34" s="74">
-        <v>1</v>
-      </c>
-      <c r="I34" s="74">
-        <v>1</v>
-      </c>
-      <c r="J34" s="76">
-        <v>0</v>
-      </c>
-      <c r="K34" s="72">
-        <v>1</v>
-      </c>
-      <c r="L34" s="83">
-        <v>1</v>
-      </c>
-      <c r="M34" s="83">
-        <v>1</v>
-      </c>
-      <c r="N34" s="84">
-        <v>1</v>
-      </c>
-      <c r="O34" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="74"/>
-      <c r="R34" s="66">
-        <f t="shared" si="0"/>
+      <c r="H34" s="73">
+        <v>1</v>
+      </c>
+      <c r="I34" s="73">
+        <v>1</v>
+      </c>
+      <c r="J34" s="75">
+        <v>0</v>
+      </c>
+      <c r="K34" s="71">
+        <v>1</v>
+      </c>
+      <c r="L34" s="82">
+        <v>1</v>
+      </c>
+      <c r="M34" s="82">
+        <v>1</v>
+      </c>
+      <c r="N34" s="83">
+        <v>1</v>
+      </c>
+      <c r="O34" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="73"/>
+      <c r="R34" s="65">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S34" s="31"/>
-      <c r="T34" s="70">
+      <c r="S34" s="30"/>
+      <c r="T34" s="69">
         <v>4</v>
       </c>
-      <c r="U34" s="44">
+      <c r="U34" s="43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="8">
+        <f t="shared" si="3"/>
+        <v>3.9000000000000004</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="12">
+        <v>3</v>
+      </c>
+      <c r="E35" s="12">
+        <v>0</v>
+      </c>
+      <c r="F35" s="12">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="73">
+        <v>1</v>
+      </c>
+      <c r="I35" s="73">
+        <v>1</v>
+      </c>
+      <c r="J35" s="75">
+        <v>1</v>
+      </c>
+      <c r="K35" s="31">
+        <v>1</v>
+      </c>
+      <c r="L35" s="82">
+        <v>1</v>
+      </c>
+      <c r="M35" s="82">
+        <v>1</v>
+      </c>
+      <c r="N35" s="83">
+        <v>1</v>
+      </c>
+      <c r="O35" s="82">
+        <v>1</v>
+      </c>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="73"/>
+      <c r="R35" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V34" s="44">
-        <f>SUMIF(U$2:U$86,"&gt;=" &amp; T34,E$2:E$86)</f>
-        <v>0</v>
-      </c>
-      <c r="W34" s="9">
-        <f>($V$17 + $V$15*U34+$V$16*V34)*(1+V$18+V$19)</f>
-        <v>3.9000000000000004</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10"/>
-      <c r="B35" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D35" s="13">
-        <v>3</v>
-      </c>
-      <c r="E35" s="13">
-        <v>0</v>
-      </c>
-      <c r="F35" s="13">
-        <f>CEILING(D35,T$22+1)</f>
-        <v>4</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="H35" s="74">
-        <v>1</v>
-      </c>
-      <c r="I35" s="74">
-        <v>1</v>
-      </c>
-      <c r="J35" s="76">
-        <v>1</v>
-      </c>
-      <c r="K35" s="32">
-        <v>1</v>
-      </c>
-      <c r="L35" s="83">
-        <v>1</v>
-      </c>
-      <c r="M35" s="83">
-        <v>1</v>
-      </c>
-      <c r="N35" s="84">
-        <v>1</v>
-      </c>
-      <c r="O35" s="83">
-        <v>1</v>
-      </c>
-      <c r="P35" s="83"/>
-      <c r="Q35" s="74"/>
-      <c r="R35" s="66">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T35" s="3"/>
       <c r="U35"/>
       <c r="V35"/>
-      <c r="W35" s="6"/>
+      <c r="W35" s="5"/>
       <c r="X35"/>
       <c r="Y35"/>
       <c r="Z35"/>
       <c r="AA35"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="12">
         <v>3</v>
       </c>
-      <c r="E36" s="13">
-        <v>0</v>
-      </c>
-      <c r="F36" s="13">
-        <f>CEILING(D36,T$22+1)</f>
+      <c r="E36" s="12">
+        <v>0</v>
+      </c>
+      <c r="F36" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="74"/>
-      <c r="J36" s="76">
-        <v>0</v>
-      </c>
-      <c r="K36" s="32">
-        <v>1</v>
-      </c>
-      <c r="L36" s="82"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="84"/>
-      <c r="O36" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="74"/>
-      <c r="R36" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S36" s="31"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="73"/>
+      <c r="J36" s="75">
+        <v>0</v>
+      </c>
+      <c r="K36" s="31">
+        <v>1</v>
+      </c>
+      <c r="L36" s="81"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="83"/>
+      <c r="O36" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="73"/>
+      <c r="R36" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S36" s="30"/>
       <c r="T36" s="3"/>
       <c r="U36"/>
       <c r="V36"/>
       <c r="W36"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="6"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+      <c r="AA36" s="5"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <v>2</v>
       </c>
-      <c r="E37" s="13">
-        <v>0</v>
-      </c>
-      <c r="F37" s="13">
-        <f>CEILING(D37,T$22+1)</f>
+      <c r="E37" s="12">
+        <v>0</v>
+      </c>
+      <c r="F37" s="12">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G37" s="21" t="s">
+      <c r="G37" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H37" s="74">
-        <v>1</v>
-      </c>
-      <c r="J37" s="76">
-        <v>1</v>
-      </c>
-      <c r="K37" s="32">
-        <v>0</v>
-      </c>
-      <c r="L37" s="82"/>
-      <c r="M37" s="83">
-        <v>1</v>
-      </c>
-      <c r="N37" s="84">
-        <v>1</v>
-      </c>
-      <c r="O37" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="74"/>
-      <c r="R37" s="66">
-        <f t="shared" si="0"/>
+      <c r="H37" s="73">
+        <v>1</v>
+      </c>
+      <c r="J37" s="75">
+        <v>1</v>
+      </c>
+      <c r="K37" s="31">
+        <v>0</v>
+      </c>
+      <c r="L37" s="81"/>
+      <c r="M37" s="82">
+        <v>1</v>
+      </c>
+      <c r="N37" s="83">
+        <v>1</v>
+      </c>
+      <c r="O37" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="73"/>
+      <c r="R37" s="65">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S37" s="31"/>
+      <c r="S37" s="30"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="31"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="12">
         <v>4</v>
       </c>
-      <c r="E38" s="13">
-        <v>0</v>
-      </c>
-      <c r="F38" s="13">
-        <f>CEILING(D38,T$22+1)</f>
+      <c r="E38" s="12">
+        <v>0</v>
+      </c>
+      <c r="F38" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="H38" s="74">
+      <c r="H38" s="73">
         <v>0.5</v>
       </c>
-      <c r="J38" s="76">
-        <v>1</v>
-      </c>
-      <c r="K38" s="32">
-        <v>0</v>
-      </c>
-      <c r="L38" s="82"/>
-      <c r="M38" s="83">
-        <v>1</v>
-      </c>
-      <c r="N38" s="84">
-        <v>1</v>
-      </c>
-      <c r="O38" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="74"/>
-      <c r="R38" s="66">
-        <f t="shared" si="0"/>
+      <c r="J38" s="75">
+        <v>1</v>
+      </c>
+      <c r="K38" s="31">
+        <v>0</v>
+      </c>
+      <c r="L38" s="81"/>
+      <c r="M38" s="82">
+        <v>1</v>
+      </c>
+      <c r="N38" s="83">
+        <v>1</v>
+      </c>
+      <c r="O38" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="73"/>
+      <c r="R38" s="65">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S38" s="31"/>
+      <c r="S38" s="30"/>
       <c r="T38" s="3"/>
       <c r="U38"/>
       <c r="V38"/>
       <c r="W38"/>
-      <c r="X38" s="31"/>
-      <c r="Y38" s="31"/>
-      <c r="Z38" s="31"/>
-      <c r="AA38" s="31"/>
+      <c r="X38" s="30"/>
+      <c r="Y38" s="30"/>
+      <c r="Z38" s="30"/>
+      <c r="AA38" s="30"/>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="12">
         <v>3</v>
       </c>
-      <c r="E39" s="13">
-        <v>0</v>
-      </c>
-      <c r="F39" s="13">
-        <f>CEILING(D39,T$22+1)</f>
+      <c r="E39" s="12">
+        <v>0</v>
+      </c>
+      <c r="F39" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="H39" s="74">
-        <v>1</v>
-      </c>
-      <c r="I39" s="74">
-        <v>1</v>
-      </c>
-      <c r="J39" s="76">
-        <v>1</v>
-      </c>
-      <c r="K39" s="32">
-        <v>0</v>
-      </c>
-      <c r="L39" s="82"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="84"/>
-      <c r="O39" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q39" s="74"/>
-      <c r="R39" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S39" s="31"/>
-      <c r="T39" s="71"/>
+      <c r="H39" s="73">
+        <v>1</v>
+      </c>
+      <c r="I39" s="73">
+        <v>1</v>
+      </c>
+      <c r="J39" s="75">
+        <v>1</v>
+      </c>
+      <c r="K39" s="31">
+        <v>0</v>
+      </c>
+      <c r="L39" s="81"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="73"/>
+      <c r="R39" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S39" s="30"/>
+      <c r="T39" s="70"/>
       <c r="U39"/>
       <c r="V39"/>
       <c r="W39"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="12">
         <v>7</v>
       </c>
-      <c r="E40" s="13">
-        <v>0</v>
-      </c>
-      <c r="F40" s="13">
-        <f>CEILING(D40,T$22+1)</f>
+      <c r="E40" s="12">
+        <v>0</v>
+      </c>
+      <c r="F40" s="12">
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G40" s="21" t="s">
+      <c r="G40" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="H40" s="74">
+      <c r="H40" s="73">
         <v>0.5</v>
       </c>
-      <c r="I40" s="74">
-        <v>1</v>
-      </c>
-      <c r="J40" s="76">
-        <v>1</v>
-      </c>
-      <c r="K40" s="32">
-        <v>1</v>
-      </c>
-      <c r="L40" s="83">
-        <v>1</v>
-      </c>
-      <c r="M40" s="83">
-        <v>1</v>
-      </c>
-      <c r="N40" s="84">
-        <v>1</v>
-      </c>
-      <c r="O40" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="80">
-        <f t="shared" si="0"/>
+      <c r="I40" s="73">
+        <v>1</v>
+      </c>
+      <c r="J40" s="75">
+        <v>1</v>
+      </c>
+      <c r="K40" s="31">
+        <v>1</v>
+      </c>
+      <c r="L40" s="82">
+        <v>1</v>
+      </c>
+      <c r="M40" s="82">
+        <v>1</v>
+      </c>
+      <c r="N40" s="83">
+        <v>1</v>
+      </c>
+      <c r="O40" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="76"/>
+      <c r="R40" s="79">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S40" s="31"/>
-      <c r="T40" s="71"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="70"/>
       <c r="U40"/>
       <c r="V40"/>
       <c r="W40"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="11">
         <v>2</v>
       </c>
-      <c r="E41" s="12">
-        <v>0</v>
-      </c>
-      <c r="F41" s="12">
-        <f>CEILING(D41,T$22+1)</f>
+      <c r="E41" s="11">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="H41" s="75">
-        <v>1</v>
-      </c>
-      <c r="I41" s="75">
-        <v>1</v>
-      </c>
-      <c r="J41" s="75">
-        <v>1</v>
-      </c>
-      <c r="K41" s="33">
-        <v>1</v>
-      </c>
-      <c r="L41" s="85">
-        <v>1</v>
-      </c>
-      <c r="M41" s="85">
-        <v>1</v>
-      </c>
-      <c r="N41" s="85">
-        <v>1</v>
-      </c>
-      <c r="O41" s="85">
-        <v>1</v>
-      </c>
-      <c r="P41" s="85"/>
-      <c r="Q41" s="76"/>
-      <c r="R41" s="66">
-        <f t="shared" si="0"/>
+      <c r="H41" s="74">
+        <v>1</v>
+      </c>
+      <c r="I41" s="74">
+        <v>1</v>
+      </c>
+      <c r="J41" s="74">
+        <v>1</v>
+      </c>
+      <c r="K41" s="32">
+        <v>1</v>
+      </c>
+      <c r="L41" s="84">
+        <v>1</v>
+      </c>
+      <c r="M41" s="84">
+        <v>1</v>
+      </c>
+      <c r="N41" s="84">
+        <v>1</v>
+      </c>
+      <c r="O41" s="84">
+        <v>1</v>
+      </c>
+      <c r="P41" s="84"/>
+      <c r="Q41" s="75"/>
+      <c r="R41" s="65">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S41" s="31"/>
-      <c r="T41" s="71"/>
+      <c r="S41" s="30"/>
+      <c r="T41" s="70"/>
       <c r="U41"/>
       <c r="V41"/>
-      <c r="W41" s="6"/>
-    </row>
-    <row r="42" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="22" t="s">
+      <c r="W41" s="5"/>
+    </row>
+    <row r="42" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="12">
         <v>5</v>
       </c>
-      <c r="E42" s="13">
-        <v>0</v>
-      </c>
-      <c r="F42" s="13">
-        <f>CEILING(D42,T$22+1)</f>
+      <c r="E42" s="12">
+        <v>0</v>
+      </c>
+      <c r="F42" s="12">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G42" s="21"/>
-      <c r="H42" s="74">
-        <v>1</v>
-      </c>
-      <c r="I42" s="74">
-        <v>1</v>
-      </c>
-      <c r="J42" s="76">
-        <v>1</v>
-      </c>
-      <c r="K42" s="32">
-        <v>1</v>
-      </c>
-      <c r="L42" s="83">
-        <v>1</v>
-      </c>
-      <c r="M42" s="83"/>
-      <c r="N42" s="84"/>
-      <c r="O42" s="83">
-        <v>1</v>
-      </c>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="74"/>
-      <c r="R42" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S42" s="31"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="73">
+        <v>1</v>
+      </c>
+      <c r="I42" s="73">
+        <v>1</v>
+      </c>
+      <c r="J42" s="75">
+        <v>1</v>
+      </c>
+      <c r="K42" s="31">
+        <v>1</v>
+      </c>
+      <c r="L42" s="82">
+        <v>1</v>
+      </c>
+      <c r="M42" s="82"/>
+      <c r="N42" s="83"/>
+      <c r="O42" s="82">
+        <v>1</v>
+      </c>
+      <c r="P42" s="82"/>
+      <c r="Q42" s="73"/>
+      <c r="R42" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S42" s="30"/>
       <c r="T42" s="3"/>
       <c r="U42"/>
       <c r="V42"/>
@@ -5316,341 +5316,341 @@
       <c r="AA42"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="12">
         <v>4</v>
       </c>
-      <c r="E43" s="13">
-        <v>0</v>
-      </c>
-      <c r="F43" s="13">
-        <f>CEILING(D43,T$22+1)</f>
+      <c r="E43" s="12">
+        <v>0</v>
+      </c>
+      <c r="F43" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G43" s="21" t="s">
+      <c r="G43" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="H43" s="74"/>
-      <c r="J43" s="76"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="82"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="84"/>
-      <c r="O43" s="83"/>
-      <c r="Q43" s="74"/>
-      <c r="R43" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="31"/>
-      <c r="T43" s="14"/>
-      <c r="U43" s="6"/>
+      <c r="H43" s="73"/>
+      <c r="J43" s="75"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="81"/>
+      <c r="M43" s="82"/>
+      <c r="N43" s="83"/>
+      <c r="O43" s="82"/>
+      <c r="Q43" s="73"/>
+      <c r="R43" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="30"/>
+      <c r="T43" s="13"/>
+      <c r="U43" s="5"/>
       <c r="V43"/>
       <c r="W43"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D44" s="12">
         <v>6</v>
       </c>
-      <c r="E44" s="13">
-        <v>0</v>
-      </c>
-      <c r="F44" s="13">
-        <f>CEILING(D44,T$22+1)</f>
+      <c r="E44" s="12">
+        <v>0</v>
+      </c>
+      <c r="F44" s="12">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G44" s="21" t="s">
+      <c r="G44" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H44" s="74">
-        <v>1</v>
-      </c>
-      <c r="I44" s="74">
-        <v>1</v>
-      </c>
-      <c r="J44" s="76">
-        <v>1</v>
-      </c>
-      <c r="K44" s="32">
-        <v>1</v>
-      </c>
-      <c r="L44" s="83">
-        <v>1</v>
-      </c>
-      <c r="M44" s="83"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="83"/>
-      <c r="Q44" s="74"/>
-      <c r="R44" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="31"/>
+      <c r="H44" s="73">
+        <v>1</v>
+      </c>
+      <c r="I44" s="73">
+        <v>1</v>
+      </c>
+      <c r="J44" s="75">
+        <v>1</v>
+      </c>
+      <c r="K44" s="31">
+        <v>1</v>
+      </c>
+      <c r="L44" s="82">
+        <v>1</v>
+      </c>
+      <c r="M44" s="82"/>
+      <c r="N44" s="83"/>
+      <c r="O44" s="82"/>
+      <c r="Q44" s="73"/>
+      <c r="R44" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="30"/>
       <c r="T44" s="3"/>
       <c r="U44"/>
       <c r="V44"/>
-      <c r="W44" s="6"/>
+      <c r="W44" s="5"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="12">
         <v>5</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="12">
         <v>2</v>
       </c>
-      <c r="F45" s="13">
-        <f>CEILING(D45,T$22+1)</f>
+      <c r="F45" s="12">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G45" s="21" t="s">
+      <c r="G45" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="H45" s="74">
-        <v>1</v>
-      </c>
-      <c r="J45" s="76">
-        <v>1</v>
-      </c>
-      <c r="K45" s="32">
-        <v>1</v>
-      </c>
-      <c r="L45" s="82"/>
-      <c r="M45" s="83">
-        <v>1</v>
-      </c>
-      <c r="N45" s="84">
-        <v>1</v>
-      </c>
-      <c r="O45" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q45" s="77"/>
-      <c r="R45" s="80">
-        <f t="shared" si="0"/>
+      <c r="H45" s="73">
+        <v>1</v>
+      </c>
+      <c r="J45" s="75">
+        <v>1</v>
+      </c>
+      <c r="K45" s="31">
+        <v>1</v>
+      </c>
+      <c r="L45" s="81"/>
+      <c r="M45" s="82">
+        <v>1</v>
+      </c>
+      <c r="N45" s="83">
+        <v>1</v>
+      </c>
+      <c r="O45" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="76"/>
+      <c r="R45" s="79">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S45" s="31"/>
+      <c r="S45" s="30"/>
       <c r="T45" s="3"/>
       <c r="U45"/>
       <c r="V45"/>
       <c r="W45"/>
     </row>
-    <row r="46" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
+    <row r="46" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="11">
         <v>7</v>
       </c>
-      <c r="E46" s="12">
-        <v>1</v>
-      </c>
-      <c r="F46" s="12">
-        <f>CEILING(D46,T$22+1)</f>
+      <c r="E46" s="11">
+        <v>1</v>
+      </c>
+      <c r="F46" s="11">
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G46" s="20" t="s">
+      <c r="G46" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="H46" s="75">
-        <v>1</v>
-      </c>
-      <c r="I46" s="75">
-        <v>1</v>
-      </c>
-      <c r="J46" s="75">
-        <v>1</v>
-      </c>
-      <c r="K46" s="33">
+      <c r="H46" s="74">
+        <v>1</v>
+      </c>
+      <c r="I46" s="74">
+        <v>1</v>
+      </c>
+      <c r="J46" s="74">
+        <v>1</v>
+      </c>
+      <c r="K46" s="32">
         <v>0.5</v>
       </c>
-      <c r="L46" s="85"/>
-      <c r="M46" s="85">
-        <v>1</v>
-      </c>
-      <c r="N46" s="85"/>
-      <c r="O46" s="85">
-        <v>1</v>
-      </c>
-      <c r="P46" s="85"/>
-      <c r="Q46" s="76"/>
-      <c r="R46" s="66">
-        <f t="shared" si="0"/>
+      <c r="L46" s="84"/>
+      <c r="M46" s="84">
+        <v>1</v>
+      </c>
+      <c r="N46" s="84"/>
+      <c r="O46" s="84">
+        <v>1</v>
+      </c>
+      <c r="P46" s="84"/>
+      <c r="Q46" s="75"/>
+      <c r="R46" s="65">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="T46" s="3"/>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A47" s="28"/>
-      <c r="B47" s="29" t="s">
+      <c r="A47" s="27"/>
+      <c r="B47" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47" s="12">
         <v>4</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="12">
         <v>2</v>
       </c>
-      <c r="F47" s="13">
-        <f>CEILING(D47,T$22+1)</f>
+      <c r="F47" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G47" s="21" t="s">
+      <c r="G47" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="H47" s="76"/>
-      <c r="I47" s="76"/>
-      <c r="J47" s="76"/>
-      <c r="K47" s="76">
+      <c r="H47" s="75"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="75"/>
+      <c r="K47" s="75">
         <v>0.5</v>
       </c>
-      <c r="L47" s="84">
-        <v>1</v>
-      </c>
-      <c r="M47" s="84"/>
-      <c r="N47" s="84">
-        <v>1</v>
-      </c>
-      <c r="O47" s="84"/>
-      <c r="P47" s="84"/>
-      <c r="Q47" s="76"/>
-      <c r="R47" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S47" s="31"/>
+      <c r="L47" s="83">
+        <v>1</v>
+      </c>
+      <c r="M47" s="83"/>
+      <c r="N47" s="83">
+        <v>1</v>
+      </c>
+      <c r="O47" s="83"/>
+      <c r="P47" s="83"/>
+      <c r="Q47" s="75"/>
+      <c r="R47" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S47" s="30"/>
       <c r="T47" s="3"/>
       <c r="U47"/>
       <c r="V47"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="6"/>
-      <c r="Y47" s="6"/>
-      <c r="Z47" s="6"/>
-      <c r="AA47" s="6"/>
-    </row>
-    <row r="48" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="10"/>
-      <c r="B48" s="22" t="s">
+      <c r="W47" s="5"/>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5"/>
+      <c r="Z47" s="5"/>
+      <c r="AA47" s="5"/>
+    </row>
+    <row r="48" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D48" s="13">
+      <c r="D48" s="12">
         <v>6</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="12">
         <v>3</v>
       </c>
-      <c r="F48" s="13">
-        <f>CEILING(D48,T$22+1)</f>
+      <c r="F48" s="12">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G48" s="21" t="s">
+      <c r="G48" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="H48" s="74">
-        <v>1</v>
-      </c>
-      <c r="I48" s="74">
-        <v>1</v>
-      </c>
-      <c r="J48" s="76">
+      <c r="H48" s="73">
+        <v>1</v>
+      </c>
+      <c r="I48" s="73">
+        <v>1</v>
+      </c>
+      <c r="J48" s="75">
         <v>0.9</v>
       </c>
-      <c r="K48" s="32">
+      <c r="K48" s="31">
         <v>0.5</v>
       </c>
-      <c r="L48" s="83"/>
-      <c r="M48" s="83">
-        <v>1</v>
-      </c>
-      <c r="N48" s="84"/>
-      <c r="O48" s="83">
-        <v>1</v>
-      </c>
-      <c r="P48" s="83"/>
-      <c r="Q48" s="74"/>
-      <c r="R48" s="66">
-        <f t="shared" si="0"/>
+      <c r="L48" s="82"/>
+      <c r="M48" s="82">
+        <v>1</v>
+      </c>
+      <c r="N48" s="83"/>
+      <c r="O48" s="82">
+        <v>1</v>
+      </c>
+      <c r="P48" s="82"/>
+      <c r="Q48" s="73"/>
+      <c r="R48" s="65">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="T48" s="3"/>
-      <c r="W48" s="6"/>
-      <c r="X48" s="6"/>
-      <c r="Y48" s="6"/>
-      <c r="Z48" s="6"/>
-      <c r="AA48" s="6"/>
-    </row>
-    <row r="49" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="10"/>
-      <c r="B49" s="22" t="s">
+      <c r="W48" s="5"/>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5"/>
+      <c r="Z48" s="5"/>
+      <c r="AA48" s="5"/>
+    </row>
+    <row r="49" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="12">
         <v>8</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="12">
         <v>4</v>
       </c>
-      <c r="F49" s="13">
-        <f>CEILING(D49,T$22+1)</f>
+      <c r="F49" s="12">
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G49" s="21" t="s">
+      <c r="G49" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="H49" s="74"/>
-      <c r="I49" s="74"/>
-      <c r="J49" s="76"/>
-      <c r="K49" s="74">
+      <c r="H49" s="73"/>
+      <c r="I49" s="73"/>
+      <c r="J49" s="75"/>
+      <c r="K49" s="73">
         <v>0.5</v>
       </c>
-      <c r="L49" s="83">
-        <v>1</v>
-      </c>
-      <c r="M49" s="83"/>
-      <c r="N49" s="84">
-        <v>1</v>
-      </c>
-      <c r="O49" s="83"/>
-      <c r="P49" s="83"/>
-      <c r="Q49" s="74"/>
-      <c r="R49" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S49" s="31"/>
-      <c r="T49" s="14"/>
+      <c r="L49" s="82">
+        <v>1</v>
+      </c>
+      <c r="M49" s="82"/>
+      <c r="N49" s="83">
+        <v>1</v>
+      </c>
+      <c r="O49" s="82"/>
+      <c r="P49" s="82"/>
+      <c r="Q49" s="73"/>
+      <c r="R49" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S49" s="30"/>
+      <c r="T49" s="13"/>
       <c r="V49"/>
       <c r="W49"/>
       <c r="X49"/>
@@ -5659,145 +5659,145 @@
       <c r="AA49"/>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B50" s="22" t="s">
+      <c r="B50" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D50" s="13">
+      <c r="D50" s="12">
         <v>2</v>
       </c>
-      <c r="E50" s="13">
-        <v>0</v>
-      </c>
-      <c r="F50" s="13">
-        <f>CEILING(D50,T$22+1)</f>
+      <c r="E50" s="12">
+        <v>0</v>
+      </c>
+      <c r="F50" s="12">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G50" s="21"/>
-      <c r="H50" s="74">
+      <c r="G50" s="20"/>
+      <c r="H50" s="73">
         <v>0.5</v>
       </c>
-      <c r="I50" s="74">
-        <v>1</v>
-      </c>
-      <c r="J50" s="76">
+      <c r="I50" s="73">
+        <v>1</v>
+      </c>
+      <c r="J50" s="75">
         <v>0.1</v>
       </c>
-      <c r="K50" s="74">
-        <v>1</v>
-      </c>
-      <c r="L50" s="83">
-        <v>1</v>
-      </c>
-      <c r="M50" s="83"/>
-      <c r="N50" s="84"/>
-      <c r="O50" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="74"/>
-      <c r="R50" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S50" s="31"/>
+      <c r="K50" s="73">
+        <v>1</v>
+      </c>
+      <c r="L50" s="82">
+        <v>1</v>
+      </c>
+      <c r="M50" s="82"/>
+      <c r="N50" s="83"/>
+      <c r="O50" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="73"/>
+      <c r="R50" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S50" s="30"/>
       <c r="T50" s="3"/>
       <c r="U50"/>
-      <c r="V50" s="6"/>
+      <c r="V50" s="5"/>
       <c r="W50"/>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D51" s="13">
+      <c r="D51" s="12">
         <v>4</v>
       </c>
-      <c r="E51" s="13">
-        <v>0</v>
-      </c>
-      <c r="F51" s="13">
-        <f>CEILING(D51,T$22+1)</f>
+      <c r="E51" s="12">
+        <v>0</v>
+      </c>
+      <c r="F51" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G51" s="21" t="s">
+      <c r="G51" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="H51" s="74"/>
-      <c r="I51" s="74">
-        <v>1</v>
-      </c>
-      <c r="J51" s="76">
-        <v>1</v>
-      </c>
-      <c r="K51" s="32"/>
-      <c r="L51" s="82"/>
-      <c r="M51" s="83">
-        <v>1</v>
-      </c>
-      <c r="N51" s="84"/>
-      <c r="O51" s="83"/>
-      <c r="Q51" s="77"/>
-      <c r="R51" s="80">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S51" s="31"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <v>1</v>
+      </c>
+      <c r="J51" s="75">
+        <v>1</v>
+      </c>
+      <c r="K51" s="31"/>
+      <c r="L51" s="81"/>
+      <c r="M51" s="82">
+        <v>1</v>
+      </c>
+      <c r="N51" s="83"/>
+      <c r="O51" s="82"/>
+      <c r="Q51" s="76"/>
+      <c r="R51" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="30"/>
       <c r="T51" s="3"/>
       <c r="U51"/>
       <c r="V51"/>
       <c r="W51"/>
     </row>
-    <row r="52" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
+    <row r="52" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="11">
         <v>2</v>
       </c>
-      <c r="E52" s="12">
-        <v>0</v>
-      </c>
-      <c r="F52" s="12">
-        <f>CEILING(D52,T$22+1)</f>
+      <c r="E52" s="11">
+        <v>0</v>
+      </c>
+      <c r="F52" s="11">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G52" s="20"/>
-      <c r="H52" s="75">
-        <v>1</v>
-      </c>
-      <c r="I52" s="75">
-        <v>1</v>
-      </c>
-      <c r="J52" s="75"/>
-      <c r="K52" s="33">
-        <v>1</v>
-      </c>
-      <c r="L52" s="85">
-        <v>1</v>
-      </c>
-      <c r="M52" s="85">
-        <v>1</v>
-      </c>
-      <c r="N52" s="85"/>
-      <c r="O52" s="85"/>
-      <c r="P52" s="85"/>
-      <c r="Q52" s="76"/>
-      <c r="R52" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="31"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="74">
+        <v>1</v>
+      </c>
+      <c r="I52" s="74">
+        <v>1</v>
+      </c>
+      <c r="J52" s="74"/>
+      <c r="K52" s="32">
+        <v>1</v>
+      </c>
+      <c r="L52" s="84">
+        <v>1</v>
+      </c>
+      <c r="M52" s="84">
+        <v>1</v>
+      </c>
+      <c r="N52" s="84"/>
+      <c r="O52" s="84"/>
+      <c r="P52" s="84"/>
+      <c r="Q52" s="75"/>
+      <c r="R52" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="30"/>
       <c r="T52" s="3"/>
       <c r="U52"/>
       <c r="V52"/>
@@ -5808,101 +5808,101 @@
       <c r="AA52"/>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D53" s="13">
+      <c r="D53" s="12">
         <v>3</v>
       </c>
-      <c r="E53" s="13">
-        <v>0</v>
-      </c>
-      <c r="F53" s="13">
-        <f>CEILING(D53,T$22+1)</f>
+      <c r="E53" s="12">
+        <v>0</v>
+      </c>
+      <c r="F53" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G53" s="21"/>
-      <c r="H53" s="74">
-        <v>1</v>
-      </c>
-      <c r="I53" s="74">
-        <v>1</v>
-      </c>
-      <c r="J53" s="76"/>
-      <c r="K53" s="32">
-        <v>1</v>
-      </c>
-      <c r="L53" s="83">
-        <v>1</v>
-      </c>
-      <c r="M53" s="83">
-        <v>1</v>
-      </c>
-      <c r="N53" s="84"/>
-      <c r="O53" s="83"/>
-      <c r="Q53" s="77"/>
-      <c r="R53" s="80">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S53" s="31"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="73">
+        <v>1</v>
+      </c>
+      <c r="I53" s="73">
+        <v>1</v>
+      </c>
+      <c r="J53" s="75"/>
+      <c r="K53" s="31">
+        <v>1</v>
+      </c>
+      <c r="L53" s="82">
+        <v>1</v>
+      </c>
+      <c r="M53" s="82">
+        <v>1</v>
+      </c>
+      <c r="N53" s="83"/>
+      <c r="O53" s="82"/>
+      <c r="Q53" s="76"/>
+      <c r="R53" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="30"/>
       <c r="T53" s="3"/>
       <c r="U53"/>
       <c r="V53"/>
       <c r="W53"/>
     </row>
-    <row r="54" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
+    <row r="54" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="11">
         <v>2</v>
       </c>
-      <c r="E54" s="12">
-        <v>0</v>
-      </c>
-      <c r="F54" s="12">
-        <f>CEILING(D54,T$22+1)</f>
+      <c r="E54" s="11">
+        <v>0</v>
+      </c>
+      <c r="F54" s="11">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G54" s="20"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="75">
-        <v>1</v>
-      </c>
-      <c r="J54" s="75">
-        <v>0</v>
-      </c>
-      <c r="K54" s="33">
-        <v>0</v>
-      </c>
-      <c r="L54" s="85">
-        <v>1</v>
-      </c>
-      <c r="M54" s="85">
-        <v>1</v>
-      </c>
-      <c r="N54" s="85">
-        <v>1</v>
-      </c>
-      <c r="O54" s="85"/>
-      <c r="P54" s="85"/>
-      <c r="Q54" s="76"/>
-      <c r="R54" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S54" s="31"/>
-      <c r="T54" s="14"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74">
+        <v>1</v>
+      </c>
+      <c r="J54" s="74">
+        <v>0</v>
+      </c>
+      <c r="K54" s="32">
+        <v>0</v>
+      </c>
+      <c r="L54" s="84">
+        <v>1</v>
+      </c>
+      <c r="M54" s="84">
+        <v>1</v>
+      </c>
+      <c r="N54" s="84">
+        <v>1</v>
+      </c>
+      <c r="O54" s="84"/>
+      <c r="P54" s="84"/>
+      <c r="Q54" s="75"/>
+      <c r="R54" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S54" s="30"/>
+      <c r="T54" s="13"/>
       <c r="W54"/>
       <c r="X54"/>
       <c r="Y54"/>
@@ -5910,881 +5910,881 @@
       <c r="AA54"/>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D55" s="13">
+      <c r="D55" s="12">
         <v>3</v>
       </c>
-      <c r="E55" s="13">
-        <v>0</v>
-      </c>
-      <c r="F55" s="13">
-        <f>CEILING(D55,T$22+1)</f>
+      <c r="E55" s="12">
+        <v>0</v>
+      </c>
+      <c r="F55" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G55" s="21"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="74">
-        <v>1</v>
-      </c>
-      <c r="J55" s="76">
-        <v>0</v>
-      </c>
-      <c r="K55" s="72">
-        <v>0</v>
-      </c>
-      <c r="L55" s="83">
-        <v>1</v>
-      </c>
-      <c r="M55" s="83">
-        <v>1</v>
-      </c>
-      <c r="N55" s="84">
-        <v>1</v>
-      </c>
-      <c r="O55" s="83">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="74"/>
-      <c r="R55" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S55" s="31"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <v>1</v>
+      </c>
+      <c r="J55" s="75">
+        <v>0</v>
+      </c>
+      <c r="K55" s="71">
+        <v>0</v>
+      </c>
+      <c r="L55" s="82">
+        <v>1</v>
+      </c>
+      <c r="M55" s="82">
+        <v>1</v>
+      </c>
+      <c r="N55" s="83">
+        <v>1</v>
+      </c>
+      <c r="O55" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="73"/>
+      <c r="R55" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S55" s="30"/>
       <c r="T55" s="3"/>
       <c r="U55"/>
       <c r="V55"/>
       <c r="W55"/>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B56" s="22" t="s">
+      <c r="B56" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D56" s="13">
+      <c r="D56" s="12">
         <v>3</v>
       </c>
-      <c r="E56" s="13">
-        <v>0</v>
-      </c>
-      <c r="F56" s="13">
-        <f>CEILING(D56,T$22+1)</f>
+      <c r="E56" s="12">
+        <v>0</v>
+      </c>
+      <c r="F56" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G56" s="21"/>
-      <c r="H56" s="74"/>
-      <c r="J56" s="76">
-        <v>0</v>
-      </c>
-      <c r="K56" s="72">
-        <v>0</v>
-      </c>
-      <c r="L56" s="83">
-        <v>1</v>
-      </c>
-      <c r="M56" s="83">
-        <v>1</v>
-      </c>
-      <c r="N56" s="84">
+      <c r="G56" s="20"/>
+      <c r="H56" s="73"/>
+      <c r="J56" s="75">
+        <v>0</v>
+      </c>
+      <c r="K56" s="71">
+        <v>0</v>
+      </c>
+      <c r="L56" s="82">
+        <v>1</v>
+      </c>
+      <c r="M56" s="82">
+        <v>1</v>
+      </c>
+      <c r="N56" s="83">
         <v>0.5</v>
       </c>
-      <c r="O56" s="83">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="74"/>
-      <c r="R56" s="66">
-        <f t="shared" si="0"/>
+      <c r="O56" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="73"/>
+      <c r="R56" s="65">
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="S56" s="31"/>
+      <c r="S56" s="30"/>
       <c r="T56" s="3"/>
       <c r="U56"/>
       <c r="V56"/>
       <c r="W56"/>
-      <c r="X56" s="31"/>
-      <c r="Y56" s="6"/>
-      <c r="Z56" s="6"/>
-      <c r="AA56" s="6"/>
+      <c r="X56" s="30"/>
+      <c r="Y56" s="5"/>
+      <c r="Z56" s="5"/>
+      <c r="AA56" s="5"/>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B57" s="22" t="s">
+      <c r="B57" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D57" s="13">
+      <c r="D57" s="12">
         <v>3</v>
       </c>
-      <c r="E57" s="13">
-        <v>0</v>
-      </c>
-      <c r="F57" s="13">
-        <f>CEILING(D57,T$22+1)</f>
+      <c r="E57" s="12">
+        <v>0</v>
+      </c>
+      <c r="F57" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G57" s="21"/>
-      <c r="H57" s="74"/>
-      <c r="J57" s="76">
-        <v>0</v>
-      </c>
-      <c r="K57" s="72">
-        <v>0</v>
-      </c>
-      <c r="L57" s="83">
-        <v>1</v>
-      </c>
-      <c r="M57" s="83"/>
-      <c r="N57" s="84"/>
-      <c r="O57" s="83"/>
-      <c r="Q57" s="74"/>
-      <c r="R57" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S57" s="31"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="73"/>
+      <c r="J57" s="75">
+        <v>0</v>
+      </c>
+      <c r="K57" s="71">
+        <v>0</v>
+      </c>
+      <c r="L57" s="82">
+        <v>1</v>
+      </c>
+      <c r="M57" s="82"/>
+      <c r="N57" s="83"/>
+      <c r="O57" s="82"/>
+      <c r="Q57" s="73"/>
+      <c r="R57" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="30"/>
       <c r="T57" s="3"/>
       <c r="U57"/>
       <c r="V57"/>
       <c r="W57"/>
-      <c r="X57" s="31"/>
+      <c r="X57" s="30"/>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B58" s="22" t="s">
+      <c r="B58" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D58" s="13">
+      <c r="D58" s="12">
         <v>2</v>
       </c>
-      <c r="E58" s="13">
-        <v>0</v>
-      </c>
-      <c r="F58" s="13">
-        <f>CEILING(D58,T$22+1)</f>
+      <c r="E58" s="12">
+        <v>0</v>
+      </c>
+      <c r="F58" s="12">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G58" s="21"/>
-      <c r="H58" s="74">
+      <c r="G58" s="20"/>
+      <c r="H58" s="73">
         <v>0.5</v>
       </c>
-      <c r="I58" s="74">
-        <v>1</v>
-      </c>
-      <c r="J58" s="76">
+      <c r="I58" s="73">
+        <v>1</v>
+      </c>
+      <c r="J58" s="75">
         <v>0.1</v>
       </c>
-      <c r="K58" s="72">
+      <c r="K58" s="71">
         <v>0.2</v>
       </c>
-      <c r="L58" s="83">
-        <v>1</v>
-      </c>
-      <c r="M58" s="83">
-        <v>1</v>
-      </c>
-      <c r="N58" s="84">
-        <v>1</v>
-      </c>
-      <c r="O58" s="83">
+      <c r="L58" s="82">
+        <v>1</v>
+      </c>
+      <c r="M58" s="82">
+        <v>1</v>
+      </c>
+      <c r="N58" s="83">
+        <v>1</v>
+      </c>
+      <c r="O58" s="82">
         <v>0.5</v>
       </c>
-      <c r="Q58" s="74"/>
-      <c r="R58" s="66">
-        <f t="shared" si="0"/>
+      <c r="Q58" s="73"/>
+      <c r="R58" s="65">
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="S58" s="31"/>
+      <c r="S58" s="30"/>
       <c r="T58" s="3"/>
       <c r="U58"/>
       <c r="V58"/>
       <c r="W58"/>
-      <c r="X58" s="31"/>
+      <c r="X58" s="30"/>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B59" s="22" t="s">
+      <c r="B59" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D59" s="13">
+      <c r="D59" s="12">
         <v>5</v>
       </c>
-      <c r="E59" s="13">
-        <v>1</v>
-      </c>
-      <c r="F59" s="13">
-        <f>CEILING(D59,T$22+1)</f>
+      <c r="E59" s="12">
+        <v>1</v>
+      </c>
+      <c r="F59" s="12">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G59" s="21"/>
-      <c r="H59" s="74">
-        <v>1</v>
-      </c>
-      <c r="I59" s="74">
-        <v>1</v>
-      </c>
-      <c r="J59" s="76">
-        <v>0</v>
-      </c>
-      <c r="K59" s="72">
-        <v>1</v>
-      </c>
-      <c r="L59" s="82"/>
-      <c r="M59" s="83">
-        <v>1</v>
-      </c>
-      <c r="N59" s="84">
-        <v>1</v>
-      </c>
-      <c r="O59" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q59" s="74"/>
-      <c r="R59" s="66">
-        <f t="shared" si="0"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="73">
+        <v>1</v>
+      </c>
+      <c r="I59" s="73">
+        <v>1</v>
+      </c>
+      <c r="J59" s="75">
+        <v>0</v>
+      </c>
+      <c r="K59" s="71">
+        <v>1</v>
+      </c>
+      <c r="L59" s="81"/>
+      <c r="M59" s="82">
+        <v>1</v>
+      </c>
+      <c r="N59" s="83">
+        <v>1</v>
+      </c>
+      <c r="O59" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="73"/>
+      <c r="R59" s="65">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S59" s="31"/>
+      <c r="S59" s="30"/>
       <c r="T59" s="3"/>
       <c r="U59"/>
-      <c r="V59" s="6"/>
+      <c r="V59" s="5"/>
       <c r="W59"/>
-      <c r="X59" s="31"/>
-    </row>
-    <row r="60" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="10"/>
+      <c r="X59" s="30"/>
+    </row>
+    <row r="60" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="9"/>
       <c r="B60" t="s">
         <v>228</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D60" s="13">
+      <c r="D60" s="12">
         <v>4</v>
       </c>
-      <c r="E60" s="13">
-        <v>0</v>
-      </c>
-      <c r="F60" s="13">
-        <f>CEILING(D60,T$22+1)</f>
+      <c r="E60" s="12">
+        <v>0</v>
+      </c>
+      <c r="F60" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G60" s="21" t="s">
+      <c r="G60" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="H60" s="74"/>
-      <c r="I60" s="74"/>
-      <c r="J60" s="76">
-        <v>1</v>
-      </c>
-      <c r="K60" s="72"/>
-      <c r="L60" s="83"/>
-      <c r="M60" s="83"/>
-      <c r="N60" s="84"/>
-      <c r="O60" s="83"/>
-      <c r="P60" s="83"/>
-      <c r="Q60" s="74"/>
-      <c r="R60" s="66">
-        <f t="shared" si="0"/>
+      <c r="H60" s="73"/>
+      <c r="I60" s="73"/>
+      <c r="J60" s="75">
+        <v>1</v>
+      </c>
+      <c r="K60" s="71"/>
+      <c r="L60" s="82"/>
+      <c r="M60" s="82"/>
+      <c r="N60" s="83"/>
+      <c r="O60" s="82"/>
+      <c r="P60" s="82"/>
+      <c r="Q60" s="73"/>
+      <c r="R60" s="65">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T60" s="3"/>
-      <c r="V60" s="6"/>
+      <c r="V60" s="5"/>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B61" s="22" t="s">
+      <c r="B61" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D61" s="13">
+      <c r="D61" s="12">
         <v>5</v>
       </c>
-      <c r="E61" s="13">
-        <v>0</v>
-      </c>
-      <c r="F61" s="13">
-        <f>CEILING(D61,T$22+1)</f>
+      <c r="E61" s="12">
+        <v>0</v>
+      </c>
+      <c r="F61" s="12">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G61" s="21"/>
-      <c r="H61" s="74">
-        <v>1</v>
-      </c>
-      <c r="J61" s="76">
+      <c r="G61" s="20"/>
+      <c r="H61" s="73">
+        <v>1</v>
+      </c>
+      <c r="J61" s="75">
         <v>0.1</v>
       </c>
-      <c r="K61" s="72">
-        <v>1</v>
-      </c>
-      <c r="L61" s="82"/>
-      <c r="M61" s="83">
-        <v>1</v>
-      </c>
-      <c r="N61" s="84">
-        <v>1</v>
-      </c>
-      <c r="O61" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="74"/>
-      <c r="R61" s="66">
-        <f t="shared" si="0"/>
+      <c r="K61" s="71">
+        <v>1</v>
+      </c>
+      <c r="L61" s="81"/>
+      <c r="M61" s="82">
+        <v>1</v>
+      </c>
+      <c r="N61" s="83">
+        <v>1</v>
+      </c>
+      <c r="O61" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="73"/>
+      <c r="R61" s="65">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S61" s="31"/>
+      <c r="S61" s="30"/>
       <c r="T61" s="3"/>
       <c r="U61"/>
       <c r="V61"/>
       <c r="W61"/>
-      <c r="X61" s="31"/>
-    </row>
-    <row r="62" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="10"/>
-      <c r="B62" s="22" t="s">
+      <c r="X61" s="30"/>
+    </row>
+    <row r="62" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9"/>
+      <c r="B62" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D62" s="13">
+      <c r="D62" s="12">
         <v>3</v>
       </c>
-      <c r="E62" s="13">
-        <v>0</v>
-      </c>
-      <c r="F62" s="13">
-        <f>CEILING(D62,T$22+1)</f>
+      <c r="E62" s="12">
+        <v>0</v>
+      </c>
+      <c r="F62" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G62" s="21" t="s">
+      <c r="G62" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="H62" s="74"/>
-      <c r="I62" s="74"/>
-      <c r="J62" s="76"/>
-      <c r="K62" s="72"/>
-      <c r="L62" s="83"/>
-      <c r="M62" s="83">
-        <v>1</v>
-      </c>
-      <c r="N62" s="84">
-        <v>1</v>
-      </c>
-      <c r="O62" s="83"/>
-      <c r="P62" s="83"/>
-      <c r="Q62" s="74"/>
-      <c r="R62" s="66">
-        <f t="shared" si="0"/>
+      <c r="H62" s="73"/>
+      <c r="I62" s="73"/>
+      <c r="J62" s="75"/>
+      <c r="K62" s="71"/>
+      <c r="L62" s="82"/>
+      <c r="M62" s="82">
+        <v>1</v>
+      </c>
+      <c r="N62" s="83">
+        <v>1</v>
+      </c>
+      <c r="O62" s="82"/>
+      <c r="P62" s="82"/>
+      <c r="Q62" s="73"/>
+      <c r="R62" s="65">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="T62" s="3"/>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D63" s="13">
-        <v>1</v>
-      </c>
-      <c r="E63" s="13">
-        <v>0</v>
-      </c>
-      <c r="F63" s="13">
-        <f>CEILING(D63,T$22+1)</f>
+      <c r="D63" s="12">
+        <v>1</v>
+      </c>
+      <c r="E63" s="12">
+        <v>0</v>
+      </c>
+      <c r="F63" s="12">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G63" s="21" t="s">
+      <c r="G63" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="H63" s="74">
-        <v>1</v>
-      </c>
-      <c r="I63" s="74">
-        <v>1</v>
-      </c>
-      <c r="J63" s="76">
-        <v>1</v>
-      </c>
-      <c r="K63" s="72">
-        <v>1</v>
-      </c>
-      <c r="L63" s="83">
-        <v>1</v>
-      </c>
-      <c r="M63" s="83">
-        <v>0</v>
-      </c>
-      <c r="N63" s="84">
-        <v>0</v>
-      </c>
-      <c r="O63" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="74"/>
-      <c r="R63" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S63" s="31"/>
+      <c r="H63" s="73">
+        <v>1</v>
+      </c>
+      <c r="I63" s="73">
+        <v>1</v>
+      </c>
+      <c r="J63" s="75">
+        <v>1</v>
+      </c>
+      <c r="K63" s="71">
+        <v>1</v>
+      </c>
+      <c r="L63" s="82">
+        <v>1</v>
+      </c>
+      <c r="M63" s="82">
+        <v>0</v>
+      </c>
+      <c r="N63" s="83">
+        <v>0</v>
+      </c>
+      <c r="O63" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="73"/>
+      <c r="R63" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S63" s="30"/>
       <c r="T63" s="3"/>
       <c r="U63"/>
       <c r="V63"/>
-      <c r="W63" s="6"/>
-      <c r="X63" s="31"/>
+      <c r="W63" s="5"/>
+      <c r="X63" s="30"/>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D64" s="13">
+      <c r="D64" s="12">
         <v>3</v>
       </c>
-      <c r="E64" s="13">
-        <v>0</v>
-      </c>
-      <c r="F64" s="13">
-        <f>CEILING(D64,T$22+1)</f>
+      <c r="E64" s="12">
+        <v>0</v>
+      </c>
+      <c r="F64" s="12">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G64" s="21" t="s">
+      <c r="G64" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="H64" s="74"/>
-      <c r="J64" s="76">
+      <c r="H64" s="73"/>
+      <c r="J64" s="75">
         <v>0.5</v>
       </c>
-      <c r="K64" s="31"/>
-      <c r="L64" s="82"/>
-      <c r="M64" s="83">
-        <v>1</v>
-      </c>
-      <c r="N64" s="84">
+      <c r="K64" s="30"/>
+      <c r="L64" s="81"/>
+      <c r="M64" s="82">
+        <v>1</v>
+      </c>
+      <c r="N64" s="83">
         <v>0.5</v>
       </c>
-      <c r="O64" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="74"/>
-      <c r="R64" s="66">
-        <f t="shared" si="0"/>
+      <c r="O64" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="73"/>
+      <c r="R64" s="65">
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="S64" s="31"/>
+      <c r="S64" s="30"/>
       <c r="T64" s="3"/>
       <c r="U64"/>
       <c r="V64"/>
       <c r="W64"/>
-      <c r="X64" s="31"/>
+      <c r="X64" s="30"/>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D65" s="13">
+      <c r="D65" s="12">
         <v>5</v>
       </c>
-      <c r="E65" s="13">
-        <v>0</v>
-      </c>
-      <c r="F65" s="13">
-        <f>CEILING(D65,T$22+1)</f>
+      <c r="E65" s="12">
+        <v>0</v>
+      </c>
+      <c r="F65" s="12">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G65" s="21" t="s">
+      <c r="G65" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H65" s="74"/>
-      <c r="I65" s="74">
-        <v>1</v>
-      </c>
-      <c r="J65" s="76">
-        <v>1</v>
-      </c>
-      <c r="K65" s="32">
-        <v>0</v>
-      </c>
-      <c r="L65" s="82"/>
-      <c r="M65" s="83">
-        <v>0</v>
-      </c>
-      <c r="N65" s="84"/>
-      <c r="O65" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="74"/>
-      <c r="R65" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S65" s="31"/>
+      <c r="H65" s="73"/>
+      <c r="I65" s="73">
+        <v>1</v>
+      </c>
+      <c r="J65" s="75">
+        <v>1</v>
+      </c>
+      <c r="K65" s="31">
+        <v>0</v>
+      </c>
+      <c r="L65" s="81"/>
+      <c r="M65" s="82">
+        <v>0</v>
+      </c>
+      <c r="N65" s="83"/>
+      <c r="O65" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="73"/>
+      <c r="R65" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S65" s="30"/>
       <c r="T65" s="3"/>
       <c r="U65"/>
       <c r="V65"/>
       <c r="W65"/>
-      <c r="X65" s="31"/>
+      <c r="X65" s="30"/>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D66" s="13">
+      <c r="D66" s="12">
         <v>9</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="12">
         <v>2</v>
       </c>
-      <c r="F66" s="13">
-        <f>CEILING(D66,T$22+1)</f>
+      <c r="F66" s="12">
+        <f t="shared" ref="F66:F85" si="6">CEILING(D66,T$22+1)</f>
         <v>10</v>
       </c>
-      <c r="G66" s="21"/>
-      <c r="H66" s="74"/>
-      <c r="J66" s="76">
-        <v>0</v>
-      </c>
-      <c r="K66" s="31"/>
-      <c r="L66" s="82"/>
-      <c r="M66" s="83"/>
-      <c r="N66" s="84">
-        <v>1</v>
-      </c>
-      <c r="O66" s="83"/>
-      <c r="Q66" s="74"/>
-      <c r="R66" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S66" s="31"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="73"/>
+      <c r="J66" s="75">
+        <v>0</v>
+      </c>
+      <c r="K66" s="30"/>
+      <c r="L66" s="81"/>
+      <c r="M66" s="82"/>
+      <c r="N66" s="83">
+        <v>1</v>
+      </c>
+      <c r="O66" s="82"/>
+      <c r="Q66" s="73"/>
+      <c r="R66" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S66" s="30"/>
       <c r="T66" s="3"/>
       <c r="U66"/>
       <c r="V66"/>
       <c r="W66"/>
-      <c r="X66" s="31"/>
-      <c r="Y66" s="6"/>
-      <c r="Z66" s="6"/>
-      <c r="AA66" s="6"/>
+      <c r="X66" s="30"/>
+      <c r="Y66" s="5"/>
+      <c r="Z66" s="5"/>
+      <c r="AA66" s="5"/>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D67" s="13">
+      <c r="D67" s="12">
         <v>7</v>
       </c>
-      <c r="E67" s="13">
-        <v>1</v>
-      </c>
-      <c r="F67" s="13">
-        <f>CEILING(D67,T$22+1)</f>
+      <c r="E67" s="12">
+        <v>1</v>
+      </c>
+      <c r="F67" s="12">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="G67" s="21"/>
-      <c r="H67" s="74"/>
-      <c r="J67" s="76"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="82"/>
-      <c r="M67" s="83">
-        <v>0</v>
-      </c>
-      <c r="N67" s="84">
-        <v>1</v>
-      </c>
-      <c r="O67" s="83"/>
-      <c r="Q67" s="74"/>
-      <c r="R67" s="66">
-        <f t="shared" ref="R67:R85" si="2">SUM(N67:Q67)</f>
-        <v>1</v>
-      </c>
-      <c r="S67" s="31"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="73"/>
+      <c r="J67" s="75"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="81"/>
+      <c r="M67" s="82">
+        <v>0</v>
+      </c>
+      <c r="N67" s="83">
+        <v>1</v>
+      </c>
+      <c r="O67" s="82"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="65">
+        <f t="shared" ref="R67:R85" si="7">SUM(N67:Q67)</f>
+        <v>1</v>
+      </c>
+      <c r="S67" s="30"/>
       <c r="T67" s="3"/>
       <c r="U67"/>
       <c r="V67"/>
-      <c r="W67" s="6"/>
-      <c r="X67" s="31"/>
+      <c r="W67" s="5"/>
+      <c r="X67" s="30"/>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B68" s="22" t="s">
+      <c r="B68" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D68" s="13">
+      <c r="D68" s="12">
         <v>5</v>
       </c>
-      <c r="E68" s="13">
-        <v>0</v>
-      </c>
-      <c r="F68" s="13">
-        <f>CEILING(D68,T$22+1)</f>
+      <c r="E68" s="12">
+        <v>0</v>
+      </c>
+      <c r="F68" s="12">
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="G68" s="21" t="s">
+      <c r="G68" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="H68" s="74"/>
-      <c r="I68" s="74">
-        <v>1</v>
-      </c>
-      <c r="J68" s="76">
-        <v>1</v>
-      </c>
-      <c r="K68" s="32"/>
-      <c r="L68" s="82"/>
-      <c r="M68" s="83">
-        <v>0</v>
-      </c>
-      <c r="N68" s="84"/>
-      <c r="O68" s="83">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="77"/>
-      <c r="R68" s="80">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="S68" s="31"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="73">
+        <v>1</v>
+      </c>
+      <c r="J68" s="75">
+        <v>1</v>
+      </c>
+      <c r="K68" s="31"/>
+      <c r="L68" s="81"/>
+      <c r="M68" s="82">
+        <v>0</v>
+      </c>
+      <c r="N68" s="83"/>
+      <c r="O68" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="76"/>
+      <c r="R68" s="79">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S68" s="30"/>
       <c r="T68" s="3"/>
       <c r="U68"/>
       <c r="V68"/>
       <c r="W68"/>
-      <c r="X68" s="31"/>
-    </row>
-    <row r="69" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
+      <c r="X68" s="30"/>
+    </row>
+    <row r="69" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="11">
         <v>3</v>
       </c>
-      <c r="E69" s="12">
-        <v>0</v>
-      </c>
-      <c r="F69" s="12">
-        <f>CEILING(D69,T$22+1)</f>
+      <c r="E69" s="11">
+        <v>0</v>
+      </c>
+      <c r="F69" s="11">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="G69" s="20"/>
-      <c r="H69" s="75"/>
-      <c r="I69" s="75">
-        <v>1</v>
-      </c>
-      <c r="J69" s="75">
+      <c r="G69" s="19"/>
+      <c r="H69" s="74"/>
+      <c r="I69" s="74">
+        <v>1</v>
+      </c>
+      <c r="J69" s="74">
         <v>0.5</v>
       </c>
-      <c r="K69" s="33"/>
-      <c r="L69" s="85">
-        <v>1</v>
-      </c>
-      <c r="M69" s="85">
-        <v>1</v>
-      </c>
-      <c r="N69" s="85">
-        <v>1</v>
-      </c>
-      <c r="O69" s="85"/>
-      <c r="P69" s="85"/>
-      <c r="Q69" s="76"/>
-      <c r="R69" s="66">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="S69" s="31"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="84">
+        <v>1</v>
+      </c>
+      <c r="M69" s="84">
+        <v>1</v>
+      </c>
+      <c r="N69" s="84">
+        <v>1</v>
+      </c>
+      <c r="O69" s="84"/>
+      <c r="P69" s="84"/>
+      <c r="Q69" s="75"/>
+      <c r="R69" s="65">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S69" s="30"/>
       <c r="T69" s="3"/>
       <c r="U69"/>
       <c r="V69"/>
       <c r="W69"/>
-      <c r="X69" s="31"/>
+      <c r="X69" s="30"/>
       <c r="Y69"/>
       <c r="Z69"/>
       <c r="AA69"/>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B70" s="22" t="s">
+      <c r="B70" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D70" s="13">
+      <c r="D70" s="12">
         <v>7</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="12">
         <v>2</v>
       </c>
-      <c r="F70" s="13">
-        <f>CEILING(D70,T$22+1)</f>
+      <c r="F70" s="12">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="G70" s="21"/>
-      <c r="H70" s="74"/>
-      <c r="J70" s="76"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="82"/>
-      <c r="M70" s="83"/>
-      <c r="N70" s="84">
-        <v>1</v>
-      </c>
-      <c r="O70" s="83"/>
-      <c r="Q70" s="74"/>
-      <c r="R70" s="66">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="S70" s="31"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="73"/>
+      <c r="J70" s="75"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="81"/>
+      <c r="M70" s="82"/>
+      <c r="N70" s="83">
+        <v>1</v>
+      </c>
+      <c r="O70" s="82"/>
+      <c r="Q70" s="73"/>
+      <c r="R70" s="65">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S70" s="30"/>
       <c r="T70" s="3"/>
       <c r="U70"/>
       <c r="V70"/>
       <c r="W70"/>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B71" s="22" t="s">
+      <c r="B71" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D71" s="13">
+      <c r="D71" s="12">
         <v>7</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="12">
         <v>2</v>
       </c>
-      <c r="F71" s="13">
-        <f>CEILING(D71,T$22+1)</f>
+      <c r="F71" s="12">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="G71" s="21"/>
-      <c r="H71" s="74"/>
-      <c r="J71" s="76"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="82"/>
-      <c r="M71" s="83"/>
-      <c r="N71" s="84"/>
-      <c r="O71" s="83"/>
-      <c r="Q71" s="74"/>
-      <c r="R71" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S71" s="31"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="73"/>
+      <c r="J71" s="75"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="81"/>
+      <c r="M71" s="82"/>
+      <c r="N71" s="83"/>
+      <c r="O71" s="82"/>
+      <c r="Q71" s="73"/>
+      <c r="R71" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S71" s="30"/>
       <c r="T71" s="3"/>
       <c r="U71"/>
       <c r="V71"/>
       <c r="W71"/>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A72" s="45"/>
-      <c r="B72" s="23" t="s">
+      <c r="A72" s="44"/>
+      <c r="B72" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="D72" s="26">
+      <c r="D72" s="25">
         <v>10</v>
       </c>
-      <c r="E72" s="26">
-        <v>0</v>
-      </c>
-      <c r="F72" s="26">
-        <f>CEILING(D72,T$22+1)</f>
+      <c r="E72" s="25">
+        <v>0</v>
+      </c>
+      <c r="F72" s="25">
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="G72" s="27"/>
-      <c r="H72" s="77"/>
-      <c r="I72" s="77">
-        <v>1</v>
-      </c>
-      <c r="J72" s="77"/>
-      <c r="K72" s="35"/>
-      <c r="L72" s="86"/>
-      <c r="M72" s="86"/>
-      <c r="N72" s="86">
-        <v>1</v>
-      </c>
-      <c r="O72" s="86"/>
-      <c r="P72" s="86"/>
-      <c r="Q72" s="77"/>
-      <c r="R72" s="80">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="S72" s="31"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="76"/>
+      <c r="I72" s="76">
+        <v>1</v>
+      </c>
+      <c r="J72" s="76"/>
+      <c r="K72" s="34"/>
+      <c r="L72" s="85"/>
+      <c r="M72" s="85"/>
+      <c r="N72" s="85">
+        <v>1</v>
+      </c>
+      <c r="O72" s="85"/>
+      <c r="P72" s="85"/>
+      <c r="Q72" s="76"/>
+      <c r="R72" s="79">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S72" s="30"/>
       <c r="T72" s="3"/>
-      <c r="U72" s="31"/>
+      <c r="U72" s="30"/>
       <c r="V72"/>
-      <c r="W72" s="6"/>
-    </row>
-    <row r="73" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="10" t="s">
+      <c r="W72" s="5"/>
+    </row>
+    <row r="73" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D73" s="13">
+      <c r="D73" s="12">
         <v>4</v>
       </c>
-      <c r="E73" s="13">
-        <v>0</v>
-      </c>
-      <c r="F73" s="13">
-        <f>CEILING(D73,T$22+1)</f>
+      <c r="E73" s="12">
+        <v>0</v>
+      </c>
+      <c r="F73" s="12">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="G73" s="21"/>
-      <c r="H73" s="74"/>
-      <c r="I73" s="74"/>
-      <c r="J73" s="76"/>
-      <c r="K73" s="31"/>
-      <c r="L73" s="83"/>
-      <c r="M73" s="83"/>
-      <c r="N73" s="84"/>
-      <c r="O73" s="82"/>
-      <c r="P73" s="83"/>
-      <c r="Q73" s="74"/>
-      <c r="R73" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S73" s="31"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="73"/>
+      <c r="I73" s="73"/>
+      <c r="J73" s="75"/>
+      <c r="K73" s="30"/>
+      <c r="L73" s="82"/>
+      <c r="M73" s="82"/>
+      <c r="N73" s="83"/>
+      <c r="O73" s="81"/>
+      <c r="P73" s="82"/>
+      <c r="Q73" s="73"/>
+      <c r="R73" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S73" s="30"/>
       <c r="T73" s="3"/>
       <c r="U73"/>
       <c r="V73"/>
@@ -6795,78 +6795,78 @@
       <c r="AA73"/>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D74" s="13">
+      <c r="D74" s="12">
         <v>3</v>
       </c>
-      <c r="E74" s="13">
-        <v>0</v>
-      </c>
-      <c r="F74" s="13">
-        <f>CEILING(D74,T$22+1)</f>
+      <c r="E74" s="12">
+        <v>0</v>
+      </c>
+      <c r="F74" s="12">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="G74" s="21"/>
-      <c r="H74" s="74"/>
-      <c r="J74" s="76"/>
-      <c r="K74" s="32"/>
-      <c r="L74" s="82"/>
-      <c r="M74" s="83"/>
-      <c r="N74" s="84"/>
-      <c r="O74" s="83"/>
-      <c r="Q74" s="74"/>
-      <c r="R74" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S74" s="31"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="73"/>
+      <c r="J74" s="75"/>
+      <c r="K74" s="31"/>
+      <c r="L74" s="81"/>
+      <c r="M74" s="82"/>
+      <c r="N74" s="83"/>
+      <c r="O74" s="82"/>
+      <c r="Q74" s="73"/>
+      <c r="R74" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S74" s="30"/>
       <c r="T74" s="3"/>
       <c r="U74"/>
       <c r="V74"/>
       <c r="W74"/>
-      <c r="X74" s="6"/>
-      <c r="Y74" s="6"/>
-      <c r="Z74" s="6"/>
-      <c r="AA74" s="6"/>
-    </row>
-    <row r="75" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="10"/>
-      <c r="B75" s="22" t="s">
+      <c r="X74" s="5"/>
+      <c r="Y74" s="5"/>
+      <c r="Z74" s="5"/>
+      <c r="AA74" s="5"/>
+    </row>
+    <row r="75" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="9"/>
+      <c r="B75" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D75" s="13">
+      <c r="D75" s="12">
         <v>4</v>
       </c>
-      <c r="E75" s="13">
-        <v>0</v>
-      </c>
-      <c r="F75" s="13">
-        <f>CEILING(D75,T$22+1)</f>
+      <c r="E75" s="12">
+        <v>0</v>
+      </c>
+      <c r="F75" s="12">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="G75" s="21" t="s">
+      <c r="G75" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-      <c r="J75" s="76"/>
-      <c r="K75" s="74"/>
-      <c r="L75" s="83"/>
-      <c r="M75" s="83"/>
-      <c r="N75" s="84"/>
-      <c r="O75" s="83"/>
-      <c r="P75" s="83"/>
-      <c r="Q75" s="77"/>
-      <c r="R75" s="80">
-        <f t="shared" si="2"/>
+      <c r="H75" s="73"/>
+      <c r="I75" s="73"/>
+      <c r="J75" s="75"/>
+      <c r="K75" s="73"/>
+      <c r="L75" s="82"/>
+      <c r="M75" s="82"/>
+      <c r="N75" s="83"/>
+      <c r="O75" s="82"/>
+      <c r="P75" s="82"/>
+      <c r="Q75" s="76"/>
+      <c r="R75" s="79">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T75" s="3"/>
@@ -6879,432 +6879,432 @@
       <c r="AA75"/>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B76" s="25" t="s">
+      <c r="B76" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C76" s="25"/>
-      <c r="D76" s="12">
+      <c r="C76" s="24"/>
+      <c r="D76" s="11">
         <v>2</v>
       </c>
-      <c r="E76" s="12">
-        <v>0</v>
-      </c>
-      <c r="F76" s="12">
-        <f>CEILING(D76,T$22+1)</f>
+      <c r="E76" s="11">
+        <v>0</v>
+      </c>
+      <c r="F76" s="11">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G76" s="20"/>
-      <c r="H76" s="75">
-        <v>1</v>
-      </c>
-      <c r="I76" s="75">
-        <v>1</v>
-      </c>
-      <c r="J76" s="75">
-        <v>0</v>
-      </c>
-      <c r="K76" s="33">
-        <v>1</v>
-      </c>
-      <c r="L76" s="85"/>
-      <c r="M76" s="85">
-        <v>1</v>
-      </c>
-      <c r="N76" s="85"/>
-      <c r="O76" s="85"/>
-      <c r="P76" s="85"/>
-      <c r="Q76" s="76"/>
-      <c r="R76" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="31"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="74">
+        <v>1</v>
+      </c>
+      <c r="I76" s="74">
+        <v>1</v>
+      </c>
+      <c r="J76" s="74">
+        <v>0</v>
+      </c>
+      <c r="K76" s="32">
+        <v>1</v>
+      </c>
+      <c r="L76" s="84"/>
+      <c r="M76" s="84">
+        <v>1</v>
+      </c>
+      <c r="N76" s="84"/>
+      <c r="O76" s="84"/>
+      <c r="P76" s="84"/>
+      <c r="Q76" s="75"/>
+      <c r="R76" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S76" s="30"/>
       <c r="T76" s="3"/>
       <c r="U76"/>
       <c r="V76"/>
       <c r="W76"/>
     </row>
-    <row r="77" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="28"/>
-      <c r="B77" s="29" t="s">
+    <row r="77" spans="1:27" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="27"/>
+      <c r="B77" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C77" s="29"/>
-      <c r="D77" s="13">
+      <c r="C77" s="28"/>
+      <c r="D77" s="12">
         <v>2</v>
       </c>
-      <c r="E77" s="13">
-        <v>1</v>
-      </c>
-      <c r="F77" s="13">
-        <f>CEILING(D77,T$22+1)</f>
+      <c r="E77" s="12">
+        <v>1</v>
+      </c>
+      <c r="F77" s="12">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G77" s="21" t="s">
+      <c r="G77" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="H77" s="76">
-        <v>1</v>
-      </c>
-      <c r="I77" s="76">
-        <v>1</v>
-      </c>
-      <c r="J77" s="76">
-        <v>1</v>
-      </c>
-      <c r="K77" s="34">
-        <v>1</v>
-      </c>
-      <c r="L77" s="84">
-        <v>1</v>
-      </c>
-      <c r="M77" s="84">
-        <v>1</v>
-      </c>
-      <c r="N77" s="84"/>
-      <c r="O77" s="84"/>
-      <c r="P77" s="84"/>
-      <c r="Q77" s="76"/>
-      <c r="R77" s="66">
-        <f t="shared" si="2"/>
+      <c r="H77" s="75">
+        <v>1</v>
+      </c>
+      <c r="I77" s="75">
+        <v>1</v>
+      </c>
+      <c r="J77" s="75">
+        <v>1</v>
+      </c>
+      <c r="K77" s="33">
+        <v>1</v>
+      </c>
+      <c r="L77" s="83">
+        <v>1</v>
+      </c>
+      <c r="M77" s="83">
+        <v>1</v>
+      </c>
+      <c r="N77" s="83"/>
+      <c r="O77" s="83"/>
+      <c r="P77" s="83"/>
+      <c r="Q77" s="75"/>
+      <c r="R77" s="65">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T77" s="3"/>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A78" s="28"/>
-      <c r="B78" s="29" t="s">
+      <c r="A78" s="27"/>
+      <c r="B78" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="C78" s="29"/>
-      <c r="D78" s="13">
-        <v>1</v>
-      </c>
-      <c r="E78" s="13">
-        <v>1</v>
-      </c>
-      <c r="F78" s="13">
-        <f>CEILING(D78,T$22+1)</f>
+      <c r="C78" s="28"/>
+      <c r="D78" s="12">
+        <v>1</v>
+      </c>
+      <c r="E78" s="12">
+        <v>1</v>
+      </c>
+      <c r="F78" s="12">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G78" s="21" t="s">
+      <c r="G78" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="H78" s="76"/>
-      <c r="I78" s="76"/>
-      <c r="J78" s="76">
-        <v>1</v>
-      </c>
-      <c r="K78" s="76"/>
-      <c r="L78" s="84">
-        <v>1</v>
-      </c>
-      <c r="M78" s="84"/>
-      <c r="N78" s="84"/>
-      <c r="O78" s="84"/>
-      <c r="P78" s="84"/>
-      <c r="Q78" s="76">
+      <c r="H78" s="75"/>
+      <c r="I78" s="75"/>
+      <c r="J78" s="75">
+        <v>1</v>
+      </c>
+      <c r="K78" s="75"/>
+      <c r="L78" s="83">
+        <v>1</v>
+      </c>
+      <c r="M78" s="83"/>
+      <c r="N78" s="83"/>
+      <c r="O78" s="83"/>
+      <c r="P78" s="83"/>
+      <c r="Q78" s="75">
         <v>2</v>
       </c>
-      <c r="R78" s="66">
-        <f t="shared" si="2"/>
+      <c r="R78" s="65">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="S78" s="31"/>
+      <c r="S78" s="30"/>
       <c r="T78" s="3"/>
-      <c r="U78" s="31"/>
-      <c r="V78" s="31"/>
-      <c r="W78" s="31"/>
-    </row>
-    <row r="79" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="10"/>
-      <c r="B79" s="22" t="s">
+      <c r="U78" s="30"/>
+      <c r="V78" s="30"/>
+      <c r="W78" s="30"/>
+    </row>
+    <row r="79" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9"/>
+      <c r="B79" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="C79" s="22"/>
-      <c r="D79" s="13">
+      <c r="C79" s="21"/>
+      <c r="D79" s="12">
         <v>4</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="12">
         <v>3</v>
       </c>
-      <c r="F79" s="13">
-        <f>CEILING(D79,T$22+1)</f>
+      <c r="F79" s="12">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="G79" s="21"/>
-      <c r="H79" s="74">
-        <v>1</v>
-      </c>
-      <c r="I79" s="74"/>
-      <c r="J79" s="76">
-        <v>1</v>
-      </c>
-      <c r="K79" s="72">
-        <v>1</v>
-      </c>
-      <c r="L79" s="83">
-        <v>1</v>
-      </c>
-      <c r="M79" s="83">
-        <v>1</v>
-      </c>
-      <c r="N79" s="84"/>
-      <c r="O79" s="72"/>
-      <c r="P79" s="83"/>
-      <c r="Q79" s="74"/>
-      <c r="R79" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S79" s="14"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="73">
+        <v>1</v>
+      </c>
+      <c r="I79" s="73"/>
+      <c r="J79" s="75">
+        <v>1</v>
+      </c>
+      <c r="K79" s="71">
+        <v>1</v>
+      </c>
+      <c r="L79" s="82">
+        <v>1</v>
+      </c>
+      <c r="M79" s="82">
+        <v>1</v>
+      </c>
+      <c r="N79" s="83"/>
+      <c r="O79" s="71"/>
+      <c r="P79" s="82"/>
+      <c r="Q79" s="73"/>
+      <c r="R79" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S79" s="13"/>
       <c r="T79" s="3"/>
       <c r="U79"/>
-      <c r="V79" s="31"/>
+      <c r="V79" s="30"/>
       <c r="W79"/>
-      <c r="X79" s="31"/>
-      <c r="Y79" s="31"/>
-      <c r="Z79" s="31"/>
-      <c r="AA79" s="31"/>
-    </row>
-    <row r="80" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="10"/>
-      <c r="B80" s="22" t="s">
+      <c r="X79" s="30"/>
+      <c r="Y79" s="30"/>
+      <c r="Z79" s="30"/>
+      <c r="AA79" s="30"/>
+    </row>
+    <row r="80" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="9"/>
+      <c r="B80" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="C80" s="22"/>
-      <c r="D80" s="13">
-        <v>1</v>
-      </c>
-      <c r="E80" s="13">
-        <v>0</v>
-      </c>
-      <c r="F80" s="13">
-        <f>CEILING(D80,T$22+1)</f>
+      <c r="C80" s="21"/>
+      <c r="D80" s="12">
+        <v>1</v>
+      </c>
+      <c r="E80" s="12">
+        <v>0</v>
+      </c>
+      <c r="F80" s="12">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G80" s="21" t="s">
+      <c r="G80" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="H80" s="74">
-        <v>1</v>
-      </c>
-      <c r="I80" s="74">
-        <v>1</v>
-      </c>
-      <c r="J80" s="76">
-        <v>1</v>
-      </c>
-      <c r="K80" s="72">
-        <v>1</v>
-      </c>
-      <c r="L80" s="83"/>
-      <c r="M80" s="83">
-        <v>1</v>
-      </c>
-      <c r="N80" s="84"/>
-      <c r="O80" s="72"/>
-      <c r="P80" s="83"/>
-      <c r="Q80" s="74"/>
-      <c r="R80" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S80" s="14"/>
+      <c r="H80" s="73">
+        <v>1</v>
+      </c>
+      <c r="I80" s="73">
+        <v>1</v>
+      </c>
+      <c r="J80" s="75">
+        <v>1</v>
+      </c>
+      <c r="K80" s="71">
+        <v>1</v>
+      </c>
+      <c r="L80" s="82"/>
+      <c r="M80" s="82">
+        <v>1</v>
+      </c>
+      <c r="N80" s="83"/>
+      <c r="O80" s="71"/>
+      <c r="P80" s="82"/>
+      <c r="Q80" s="73"/>
+      <c r="R80" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S80" s="13"/>
       <c r="T80" s="3"/>
-      <c r="U80" s="31"/>
-      <c r="V80" s="31"/>
-      <c r="W80" s="31"/>
-      <c r="X80" s="31"/>
-      <c r="Y80" s="31"/>
-      <c r="Z80" s="31"/>
-      <c r="AA80" s="31"/>
+      <c r="U80" s="30"/>
+      <c r="V80" s="30"/>
+      <c r="W80" s="30"/>
+      <c r="X80" s="30"/>
+      <c r="Y80" s="30"/>
+      <c r="Z80" s="30"/>
+      <c r="AA80" s="30"/>
     </row>
     <row r="81" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B81" s="22" t="s">
+      <c r="B81" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="D81" s="13">
-        <v>1</v>
-      </c>
-      <c r="E81" s="13">
-        <v>1</v>
-      </c>
-      <c r="F81" s="13">
-        <f>CEILING(D81,T$22+1)</f>
+      <c r="D81" s="12">
+        <v>1</v>
+      </c>
+      <c r="E81" s="12">
+        <v>1</v>
+      </c>
+      <c r="F81" s="12">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G81" s="21" t="s">
+      <c r="G81" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="H81" s="74"/>
-      <c r="J81" s="76">
-        <v>1</v>
-      </c>
-      <c r="K81" s="72"/>
-      <c r="L81" s="82"/>
-      <c r="M81" s="83"/>
-      <c r="N81" s="84"/>
-      <c r="O81" s="72"/>
-      <c r="Q81" s="74"/>
-      <c r="R81" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S81" s="14"/>
+      <c r="H81" s="73"/>
+      <c r="J81" s="75">
+        <v>1</v>
+      </c>
+      <c r="K81" s="71"/>
+      <c r="L81" s="81"/>
+      <c r="M81" s="82"/>
+      <c r="N81" s="83"/>
+      <c r="O81" s="71"/>
+      <c r="Q81" s="73"/>
+      <c r="R81" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S81" s="13"/>
       <c r="T81" s="3"/>
       <c r="U81"/>
       <c r="V81"/>
       <c r="W81"/>
     </row>
     <row r="82" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B82" s="22" t="s">
+      <c r="B82" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="D82" s="13">
+      <c r="D82" s="12">
         <v>3</v>
       </c>
-      <c r="E82" s="13">
-        <v>1</v>
-      </c>
-      <c r="F82" s="13">
-        <f>CEILING(D82,T$22+1)</f>
+      <c r="E82" s="12">
+        <v>1</v>
+      </c>
+      <c r="F82" s="12">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="G82" s="21"/>
-      <c r="H82" s="74"/>
-      <c r="J82" s="76"/>
-      <c r="L82" s="82"/>
-      <c r="M82" s="83"/>
-      <c r="N82" s="84"/>
-      <c r="O82" s="83"/>
-      <c r="Q82" s="74"/>
-      <c r="R82" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S82" s="14"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="73"/>
+      <c r="J82" s="75"/>
+      <c r="L82" s="81"/>
+      <c r="M82" s="82"/>
+      <c r="N82" s="83"/>
+      <c r="O82" s="82"/>
+      <c r="Q82" s="73"/>
+      <c r="R82" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S82" s="13"/>
       <c r="T82" s="3"/>
       <c r="U82"/>
       <c r="V82"/>
       <c r="W82"/>
-      <c r="X82" s="6"/>
-      <c r="Y82" s="6"/>
-      <c r="Z82" s="6"/>
-      <c r="AA82" s="6"/>
+      <c r="X82" s="5"/>
+      <c r="Y82" s="5"/>
+      <c r="Z82" s="5"/>
+      <c r="AA82" s="5"/>
     </row>
     <row r="83" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="D83" s="13">
-        <v>1</v>
-      </c>
-      <c r="E83" s="13">
-        <v>0</v>
-      </c>
-      <c r="F83" s="13">
-        <f>CEILING(D83,T$22+1)</f>
+      <c r="D83" s="12">
+        <v>1</v>
+      </c>
+      <c r="E83" s="12">
+        <v>0</v>
+      </c>
+      <c r="F83" s="12">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G83" s="21"/>
-      <c r="H83" s="74"/>
-      <c r="J83" s="76"/>
-      <c r="L83" s="82"/>
-      <c r="M83" s="83"/>
-      <c r="N83" s="84"/>
-      <c r="O83" s="83"/>
-      <c r="Q83" s="74"/>
-      <c r="R83" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S83" s="14"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="73"/>
+      <c r="J83" s="75"/>
+      <c r="L83" s="81"/>
+      <c r="M83" s="82"/>
+      <c r="N83" s="83"/>
+      <c r="O83" s="82"/>
+      <c r="Q83" s="73"/>
+      <c r="R83" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S83" s="13"/>
       <c r="T83" s="3"/>
       <c r="U83"/>
       <c r="V83"/>
       <c r="W83"/>
     </row>
-    <row r="84" spans="1:30" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="10"/>
-      <c r="B84" s="22" t="s">
+    <row r="84" spans="1:30" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="9"/>
+      <c r="B84" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C84" s="22"/>
-      <c r="D84" s="13">
+      <c r="C84" s="21"/>
+      <c r="D84" s="12">
         <v>4</v>
       </c>
-      <c r="E84" s="13">
-        <v>0</v>
-      </c>
-      <c r="F84" s="13">
-        <f>CEILING(D84,T$22+1)</f>
+      <c r="E84" s="12">
+        <v>0</v>
+      </c>
+      <c r="F84" s="12">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="G84" s="21"/>
-      <c r="H84" s="74"/>
-      <c r="I84" s="74"/>
-      <c r="J84" s="76"/>
-      <c r="K84" s="74"/>
-      <c r="L84" s="83"/>
-      <c r="M84" s="83"/>
-      <c r="N84" s="84"/>
-      <c r="O84" s="83"/>
-      <c r="P84" s="83"/>
-      <c r="Q84" s="74"/>
-      <c r="R84" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S84" s="14"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="73"/>
+      <c r="I84" s="73"/>
+      <c r="J84" s="75"/>
+      <c r="K84" s="73"/>
+      <c r="L84" s="82"/>
+      <c r="M84" s="82"/>
+      <c r="N84" s="83"/>
+      <c r="O84" s="82"/>
+      <c r="P84" s="82"/>
+      <c r="Q84" s="73"/>
+      <c r="R84" s="65">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S84" s="13"/>
       <c r="T84" s="3"/>
       <c r="U84"/>
       <c r="V84"/>
       <c r="W84"/>
-      <c r="X84" s="6"/>
-      <c r="Y84" s="6"/>
-      <c r="Z84" s="6"/>
-      <c r="AA84" s="6"/>
+      <c r="X84" s="5"/>
+      <c r="Y84" s="5"/>
+      <c r="Z84" s="5"/>
+      <c r="AA84" s="5"/>
     </row>
     <row r="85" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B85" s="23" t="s">
+      <c r="B85" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="C85" s="23"/>
-      <c r="D85" s="26">
-        <v>1</v>
-      </c>
-      <c r="E85" s="26">
-        <v>0</v>
-      </c>
-      <c r="F85" s="26">
-        <f>CEILING(D85,T$22+1)</f>
+      <c r="C85" s="22"/>
+      <c r="D85" s="25">
+        <v>1</v>
+      </c>
+      <c r="E85" s="25">
+        <v>0</v>
+      </c>
+      <c r="F85" s="25">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G85" s="27" t="s">
+      <c r="G85" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="H85" s="77"/>
-      <c r="I85" s="77">
-        <v>1</v>
-      </c>
-      <c r="J85" s="77"/>
-      <c r="K85" s="35">
-        <v>1</v>
-      </c>
-      <c r="L85" s="86"/>
-      <c r="M85" s="86">
-        <v>1</v>
-      </c>
-      <c r="N85" s="86"/>
-      <c r="O85" s="86"/>
-      <c r="P85" s="86"/>
-      <c r="Q85" s="77"/>
-      <c r="R85" s="80">
-        <f t="shared" si="2"/>
+      <c r="H85" s="76"/>
+      <c r="I85" s="76">
+        <v>1</v>
+      </c>
+      <c r="J85" s="76"/>
+      <c r="K85" s="34">
+        <v>1</v>
+      </c>
+      <c r="L85" s="85"/>
+      <c r="M85" s="85">
+        <v>1</v>
+      </c>
+      <c r="N85" s="85"/>
+      <c r="O85" s="85"/>
+      <c r="P85" s="85"/>
+      <c r="Q85" s="76"/>
+      <c r="R85" s="79">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S85" s="3"/>
@@ -7314,206 +7314,206 @@
       <c r="W85"/>
     </row>
     <row r="86" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="11"/>
-      <c r="X86" s="31"/>
-      <c r="Y86" s="31"/>
-      <c r="Z86" s="31"/>
-      <c r="AA86" s="6"/>
-      <c r="AB86" s="6"/>
-      <c r="AC86" s="6"/>
-      <c r="AD86" s="6"/>
+      <c r="A86" s="10"/>
+      <c r="X86" s="30"/>
+      <c r="Y86" s="30"/>
+      <c r="Z86" s="30"/>
+      <c r="AA86" s="5"/>
+      <c r="AB86" s="5"/>
+      <c r="AC86" s="5"/>
+      <c r="AD86" s="5"/>
     </row>
     <row r="87" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="G87" s="81"/>
-      <c r="H87" s="62"/>
-      <c r="I87" s="62"/>
-      <c r="J87" s="62"/>
-      <c r="K87" s="59" t="s">
+      <c r="G87" s="80"/>
+      <c r="H87" s="61"/>
+      <c r="I87" s="61"/>
+      <c r="J87" s="61"/>
+      <c r="K87" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="L87" s="60"/>
-      <c r="M87" s="60">
+      <c r="L87" s="59"/>
+      <c r="M87" s="59">
         <f t="array" ref="M87">SUM($F2:$F85*(K2:K85&gt;=0.9)*($R2:$R85&gt;=$T$12))</f>
         <v>82</v>
       </c>
-      <c r="N87" s="60" t="e">
+      <c r="N87" s="59" t="e">
         <f t="array" ref="N87">SUM($F2:$F85*(#REF!&gt;=0.9)*($R2:$R85&gt;=$T$12))</f>
         <v>#REF!</v>
       </c>
-      <c r="O87" s="60">
+      <c r="O87" s="59">
         <f t="array" ref="O87">SUM($F2:$F85*(L2:L85&gt;=0.9)*($R2:$R85&gt;=$T$12))</f>
         <v>66</v>
       </c>
-      <c r="P87" s="62"/>
-      <c r="Q87" s="62"/>
-      <c r="R87" s="62"/>
-      <c r="S87" s="62"/>
-      <c r="T87" s="62"/>
-      <c r="AA87" s="6"/>
-      <c r="AB87" s="6"/>
-      <c r="AC87" s="6"/>
-      <c r="AD87" s="6"/>
+      <c r="P87" s="61"/>
+      <c r="Q87" s="61"/>
+      <c r="R87" s="61"/>
+      <c r="S87" s="61"/>
+      <c r="T87" s="61"/>
+      <c r="AA87" s="5"/>
+      <c r="AB87" s="5"/>
+      <c r="AC87" s="5"/>
+      <c r="AD87" s="5"/>
     </row>
     <row r="88" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="G88" s="81"/>
-      <c r="H88" s="62"/>
-      <c r="I88" s="62"/>
-      <c r="J88" s="62"/>
-      <c r="K88" s="61" t="s">
+      <c r="G88" s="80"/>
+      <c r="H88" s="61"/>
+      <c r="I88" s="61"/>
+      <c r="J88" s="61"/>
+      <c r="K88" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="L88" s="62"/>
-      <c r="M88" s="62">
+      <c r="L88" s="61"/>
+      <c r="M88" s="61">
         <f t="array" ref="M88">SUM($F2:$F85*K2:K85*($R2:$R85&gt;=$T$12))</f>
         <v>82.4</v>
       </c>
-      <c r="N88" s="62" t="e">
+      <c r="N88" s="61" t="e">
         <f t="array" ref="N88">SUM($F2:$F85*#REF!*($R2:$R85&gt;=$T$12))</f>
         <v>#REF!</v>
       </c>
-      <c r="O88" s="62">
+      <c r="O88" s="61">
         <f t="array" ref="O88">SUM($F2:$F85*L2:L85*($R2:$R85&gt;=$T$12))</f>
         <v>66.400000000000006</v>
       </c>
-      <c r="P88" s="62"/>
-      <c r="Q88" s="62"/>
-      <c r="R88" s="62"/>
-      <c r="S88" s="62"/>
-      <c r="T88" s="62"/>
+      <c r="P88" s="61"/>
+      <c r="Q88" s="61"/>
+      <c r="R88" s="61"/>
+      <c r="S88" s="61"/>
+      <c r="T88" s="61"/>
     </row>
     <row r="89" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="G89" s="81"/>
-      <c r="H89" s="62"/>
-      <c r="I89" s="62"/>
-      <c r="J89" s="62"/>
-      <c r="K89" s="61" t="s">
+      <c r="G89" s="80"/>
+      <c r="H89" s="61"/>
+      <c r="I89" s="61"/>
+      <c r="J89" s="61"/>
+      <c r="K89" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="L89" s="62"/>
-      <c r="M89" s="62">
+      <c r="L89" s="61"/>
+      <c r="M89" s="61">
         <f t="array" ref="M89">SUM($F$2:$F$85*(K$2:K$85&gt;=0.1)*($R$2:$R$85&gt;=$T$12))</f>
         <v>84</v>
       </c>
-      <c r="N89" s="62" t="e">
+      <c r="N89" s="61" t="e">
         <f t="array" ref="N89">SUM($F$2:$F$85*(#REF!&gt;=0.1)*($R$2:$R$85&gt;=$T$12))</f>
         <v>#REF!</v>
       </c>
-      <c r="O89" s="62">
+      <c r="O89" s="61">
         <f t="array" ref="O89">SUM($F$2:$F$85*(L$2:L$85&gt;=0.1)*($R$2:$R$85&gt;=$T$12))</f>
         <v>70</v>
       </c>
-      <c r="P89" s="62"/>
-      <c r="Q89" s="62"/>
-      <c r="R89" s="62"/>
-      <c r="S89" s="62"/>
-      <c r="T89" s="62"/>
+      <c r="P89" s="61"/>
+      <c r="Q89" s="61"/>
+      <c r="R89" s="61"/>
+      <c r="S89" s="61"/>
+      <c r="T89" s="61"/>
     </row>
     <row r="90" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="G90" s="81"/>
-      <c r="H90" s="62"/>
-      <c r="I90" s="62"/>
-      <c r="J90" s="62"/>
-      <c r="K90" s="61" t="s">
+      <c r="G90" s="80"/>
+      <c r="H90" s="61"/>
+      <c r="I90" s="61"/>
+      <c r="J90" s="61"/>
+      <c r="K90" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="L90" s="62"/>
-      <c r="M90" s="62">
+      <c r="L90" s="61"/>
+      <c r="M90" s="61">
         <f>LOOKUP($T$12,$T26:$T34,$U26:$U34)</f>
         <v>106</v>
       </c>
-      <c r="N90" s="62">
+      <c r="N90" s="61">
         <f>LOOKUP($T$12,$T26:$T34,$U26:$U34)</f>
         <v>106</v>
       </c>
-      <c r="O90" s="62">
+      <c r="O90" s="61">
         <f>LOOKUP($T$12,$T26:$T34,$U26:$U34)</f>
         <v>106</v>
       </c>
-      <c r="P90" s="62"/>
-      <c r="Q90" s="62"/>
-      <c r="R90" s="62"/>
-      <c r="S90" s="62"/>
-      <c r="T90" s="62"/>
+      <c r="P90" s="61"/>
+      <c r="Q90" s="61"/>
+      <c r="R90" s="61"/>
+      <c r="S90" s="61"/>
+      <c r="T90" s="61"/>
     </row>
     <row r="91" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="G91" s="81"/>
-      <c r="H91" s="63"/>
-      <c r="I91" s="63"/>
-      <c r="J91" s="63"/>
-      <c r="K91" s="61" t="s">
+      <c r="G91" s="80"/>
+      <c r="H91" s="62"/>
+      <c r="I91" s="62"/>
+      <c r="J91" s="62"/>
+      <c r="K91" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="L91" s="63"/>
-      <c r="M91" s="63">
+      <c r="L91" s="62"/>
+      <c r="M91" s="62">
         <f>M88/M90</f>
         <v>0.77735849056603779</v>
       </c>
-      <c r="N91" s="63" t="e">
-        <f t="shared" ref="N91:O91" si="3">N88/N90</f>
+      <c r="N91" s="62" t="e">
+        <f t="shared" ref="N91:O91" si="8">N88/N90</f>
         <v>#REF!</v>
       </c>
-      <c r="O91" s="63">
-        <f t="shared" si="3"/>
+      <c r="O91" s="62">
+        <f t="shared" si="8"/>
         <v>0.62641509433962272</v>
       </c>
-      <c r="P91" s="63"/>
-      <c r="Q91" s="63"/>
-      <c r="R91" s="63"/>
-      <c r="S91" s="63"/>
-      <c r="T91" s="63"/>
-      <c r="Z91" s="31"/>
+      <c r="P91" s="62"/>
+      <c r="Q91" s="62"/>
+      <c r="R91" s="62"/>
+      <c r="S91" s="62"/>
+      <c r="T91" s="62"/>
+      <c r="Z91" s="30"/>
     </row>
     <row r="92" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D92" s="31"/>
-      <c r="G92" s="81"/>
-      <c r="H92" s="62"/>
-      <c r="I92" s="62"/>
-      <c r="J92" s="62"/>
-      <c r="K92" s="64" t="s">
+      <c r="D92" s="30"/>
+      <c r="G92" s="80"/>
+      <c r="H92" s="61"/>
+      <c r="I92" s="61"/>
+      <c r="J92" s="61"/>
+      <c r="K92" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="L92" s="65"/>
-      <c r="M92" s="65">
+      <c r="L92" s="64"/>
+      <c r="M92" s="64">
         <f t="array" ref="M92">SUM($F2:$F85*K2:K85*($R2:$R85&lt;$T$12))</f>
         <v>77</v>
       </c>
-      <c r="N92" s="65" t="e">
+      <c r="N92" s="64" t="e">
         <f t="array" ref="N92">SUM($F2:$F85*#REF!*($R2:$R85&lt;$T$12))</f>
         <v>#REF!</v>
       </c>
-      <c r="O92" s="65">
+      <c r="O92" s="64">
         <f t="array" ref="O92">SUM($F2:$F85*L2:L85*($R2:$R85&lt;$T$12))</f>
         <v>88</v>
       </c>
-      <c r="P92" s="62"/>
-      <c r="Q92" s="62"/>
-      <c r="R92" s="62"/>
-      <c r="S92" s="62"/>
-      <c r="T92" s="62"/>
+      <c r="P92" s="61"/>
+      <c r="Q92" s="61"/>
+      <c r="R92" s="61"/>
+      <c r="S92" s="61"/>
+      <c r="T92" s="61"/>
     </row>
     <row r="93" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="D93" s="31"/>
-    </row>
-    <row r="94" spans="1:30" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="10"/>
-      <c r="B94" s="22"/>
-      <c r="C94" s="22"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="19"/>
+      <c r="D93" s="30"/>
+    </row>
+    <row r="94" spans="1:30" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="9"/>
+      <c r="B94" s="21"/>
+      <c r="C94" s="21"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="18"/>
       <c r="H94" s="2"/>
-      <c r="I94" s="74"/>
-      <c r="J94" s="74"/>
-      <c r="K94" s="74"/>
-      <c r="L94" s="74"/>
+      <c r="I94" s="73"/>
+      <c r="J94" s="73"/>
+      <c r="K94" s="73"/>
+      <c r="L94" s="73"/>
       <c r="M94" s="2"/>
-      <c r="N94" s="74"/>
-      <c r="O94" s="74"/>
-      <c r="P94" s="83"/>
-      <c r="Q94" s="83"/>
-      <c r="R94" s="83"/>
-      <c r="S94" s="83"/>
-      <c r="T94" s="74"/>
+      <c r="N94" s="73"/>
+      <c r="O94" s="73"/>
+      <c r="P94" s="82"/>
+      <c r="Q94" s="82"/>
+      <c r="R94" s="82"/>
+      <c r="S94" s="82"/>
+      <c r="T94" s="73"/>
       <c r="U94" s="3"/>
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
@@ -7526,31 +7526,31 @@
       <c r="AD94"/>
     </row>
     <row r="95" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="D95" s="31"/>
+      <c r="D95" s="30"/>
     </row>
     <row r="100" spans="27:30" x14ac:dyDescent="0.3">
-      <c r="AA100" s="6"/>
-      <c r="AB100" s="6"/>
-      <c r="AC100" s="6"/>
-      <c r="AD100" s="6"/>
+      <c r="AA100" s="5"/>
+      <c r="AB100" s="5"/>
+      <c r="AC100" s="5"/>
+      <c r="AD100" s="5"/>
     </row>
     <row r="104" spans="27:30" x14ac:dyDescent="0.3">
-      <c r="AA104" s="6"/>
-      <c r="AB104" s="6"/>
-      <c r="AC104" s="6"/>
-      <c r="AD104" s="6"/>
+      <c r="AA104" s="5"/>
+      <c r="AB104" s="5"/>
+      <c r="AC104" s="5"/>
+      <c r="AD104" s="5"/>
     </row>
     <row r="109" spans="27:30" x14ac:dyDescent="0.3">
-      <c r="AA109" s="6"/>
-      <c r="AB109" s="6"/>
-      <c r="AC109" s="6"/>
-      <c r="AD109" s="6"/>
+      <c r="AA109" s="5"/>
+      <c r="AB109" s="5"/>
+      <c r="AC109" s="5"/>
+      <c r="AD109" s="5"/>
     </row>
     <row r="122" spans="27:30" x14ac:dyDescent="0.3">
-      <c r="AA122" s="31"/>
-      <c r="AB122" s="31"/>
-      <c r="AC122" s="31"/>
-      <c r="AD122" s="31"/>
+      <c r="AA122" s="30"/>
+      <c r="AB122" s="30"/>
+      <c r="AC122" s="30"/>
+      <c r="AD122" s="30"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q2:R85 B2:M85 N2:N72 P2:P72">
